--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47637,6 +47637,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2056">
+      <c r="A2056" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2056" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2056" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2056" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2056" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2056" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47660,6 +47660,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2057">
+      <c r="A2057" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2057" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2057" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2057" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47683,6 +47683,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2058">
+      <c r="A2058" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2058" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2058" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2058" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2058" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47706,6 +47706,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2059">
+      <c r="A2059" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2059" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2059" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2059" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47570,7 +47570,7 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2053" t="n">
         <v>0</v>
@@ -47593,7 +47593,7 @@
     </row>
     <row r="2054">
       <c r="A2054" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2054" t="n">
         <v>0</v>
@@ -47616,7 +47616,7 @@
     </row>
     <row r="2055">
       <c r="A2055" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2055" t="n">
         <v>0</v>
@@ -47639,7 +47639,7 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2056" t="n">
         <v>0</v>
@@ -47662,7 +47662,7 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2057" t="n">
         <v>0</v>
@@ -47685,7 +47685,7 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2058" t="n">
         <v>0</v>
@@ -47708,7 +47708,7 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2059" t="n">
         <v>0</v>
@@ -47726,6 +47726,29 @@
         <v>0.939000010490417</v>
       </c>
       <c r="G2059" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2060" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2060" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2060" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47752,6 +47752,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2061">
+      <c r="A2061" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2061" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2061" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2061" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2062" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2062" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2062" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47798,6 +47798,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2063">
+      <c r="A2063" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B2063" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2063" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2063" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47821,6 +47821,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2064">
+      <c r="A2064" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2064" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2064" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2064" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2064" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2064" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47844,6 +47844,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2065">
+      <c r="A2065" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2065" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2065" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2065" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47867,6 +47867,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2066">
+      <c r="A2066" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2066" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2066" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2066" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47890,6 +47890,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2067" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47913,6 +47913,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2068" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47936,6 +47936,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2069" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2069" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2069" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47959,6 +47959,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2070">
+      <c r="A2070" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2070" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2070" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2070" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -47982,6 +47982,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2071">
+      <c r="A2071" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2071" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2071" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2071" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48005,6 +48005,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2072" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2072" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2072" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48028,6 +48028,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2073" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2073" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2073" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48051,6 +48051,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2074">
+      <c r="A2074" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2074" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2074" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2074" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48074,6 +48074,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2075" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48097,6 +48097,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2076" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2076" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2076" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48143,6 +48143,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48166,6 +48166,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2079" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48189,6 +48189,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2080" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -48212,6 +48212,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2081">
+      <c r="A2081" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2081" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2081" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2081" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2081" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -60756,6 +60756,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2083">
+      <c r="A2083" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2083" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2083" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2083" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -543,7 +543,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989003777503967</v>
+        <v>0.989003837108612</v>
       </c>
       <c r="H6" t="n">
         <v>114000</v>
@@ -630,7 +630,7 @@
         <v>0.954100012779236</v>
       </c>
       <c r="G9" t="n">
-        <v>0.868085145950317</v>
+        <v>0.868085086345673</v>
       </c>
       <c r="H9" t="n">
         <v>39000</v>
@@ -659,7 +659,7 @@
         <v>0.981899976730347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.893378853797913</v>
+        <v>0.893378794193268</v>
       </c>
       <c r="H10" t="n">
         <v>23000</v>
@@ -1007,7 +1007,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G22" t="n">
-        <v>1.00902044773102</v>
+        <v>1.00902032852173</v>
       </c>
       <c r="H22" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H26" t="n">
         <v>1000</v>
@@ -1152,7 +1152,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G27" t="n">
-        <v>0.983908712863922</v>
+        <v>0.983908593654633</v>
       </c>
       <c r="H27" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G28" t="n">
-        <v>0.983908712863922</v>
+        <v>0.983908593654633</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G29" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H29" t="n">
         <v>34000</v>
@@ -1326,7 +1326,7 @@
         <v>1.08519995212555</v>
       </c>
       <c r="G33" t="n">
-        <v>0.987365961074829</v>
+        <v>0.987366020679474</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G35" t="n">
-        <v>1.02685344219208</v>
+        <v>1.02685332298279</v>
       </c>
       <c r="H35" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G36" t="n">
-        <v>1.02685344219208</v>
+        <v>1.02685332298279</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G37" t="n">
-        <v>1.02685344219208</v>
+        <v>1.02685332298279</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G39" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H39" t="n">
         <v>14000</v>
@@ -1529,7 +1529,7 @@
         <v>1.0654000043869</v>
       </c>
       <c r="G40" t="n">
-        <v>0.969351053237915</v>
+        <v>0.96935111284256</v>
       </c>
       <c r="H40" t="n">
         <v>5000</v>
@@ -1587,7 +1587,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G42" t="n">
-        <v>0.980815052986145</v>
+        <v>0.98081511259079</v>
       </c>
       <c r="H42" t="n">
         <v>55000</v>
@@ -1616,7 +1616,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>0.907117545604706</v>
+        <v>0.907117486000061</v>
       </c>
       <c r="H43" t="n">
         <v>60000</v>
@@ -2138,7 +2138,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G61" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H61" t="n">
         <v>3000</v>
@@ -2660,7 +2660,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>0.826141178607941</v>
+        <v>0.826141119003296</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G80" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H80" t="n">
         <v>21000</v>
@@ -2718,7 +2718,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G81" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G82" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2776,7 +2776,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G83" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>0.802500009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>0.730152249336243</v>
+        <v>0.730152308940887</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G91" t="n">
-        <v>0.713320076465607</v>
+        <v>0.713320136070251</v>
       </c>
       <c r="H91" t="n">
         <v>11000</v>
@@ -3037,7 +3037,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G92" t="n">
-        <v>0.68966406583786</v>
+        <v>0.689664125442505</v>
       </c>
       <c r="H92" t="n">
         <v>36000</v>
@@ -3066,7 +3066,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G93" t="n">
-        <v>0.707861065864563</v>
+        <v>0.707861006259918</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>0.67328679561615</v>
+        <v>0.673286855220795</v>
       </c>
       <c r="H95" t="n">
         <v>2000</v>
@@ -3269,7 +3269,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G100" t="n">
-        <v>0.693303525447845</v>
+        <v>0.693303465843201</v>
       </c>
       <c r="H100" t="n">
         <v>2000</v>
@@ -3298,7 +3298,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G101" t="n">
-        <v>0.704221606254578</v>
+        <v>0.704221665859222</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G102" t="n">
-        <v>0.704221606254578</v>
+        <v>0.704221665859222</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G103" t="n">
-        <v>0.704221606254578</v>
+        <v>0.704221665859222</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G111" t="n">
-        <v>0.580027461051941</v>
+        <v>0.580027520656586</v>
       </c>
       <c r="H111" t="n">
         <v>17000</v>
@@ -3675,7 +3675,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G114" t="n">
-        <v>0.576843023300171</v>
+        <v>0.576843082904816</v>
       </c>
       <c r="H114" t="n">
         <v>3000</v>
@@ -3733,7 +3733,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>0.564105212688446</v>
+        <v>0.564105153083801</v>
       </c>
       <c r="H116" t="n">
         <v>3000</v>
@@ -3820,7 +3820,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G119" t="n">
-        <v>0.624155044555664</v>
+        <v>0.624155104160309</v>
       </c>
       <c r="H119" t="n">
         <v>58000</v>
@@ -3878,7 +3878,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G121" t="n">
-        <v>0.61869603395462</v>
+        <v>0.618695974349976</v>
       </c>
       <c r="H121" t="n">
         <v>8000</v>
@@ -3965,7 +3965,7 @@
         <v>0.676999986171722</v>
       </c>
       <c r="G124" t="n">
-        <v>0.615966439247131</v>
+        <v>0.615966498851776</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G125" t="n">
-        <v>0.595040023326874</v>
+        <v>0.595039963722229</v>
       </c>
       <c r="H125" t="n">
         <v>5000</v>
@@ -4052,7 +4052,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G127" t="n">
-        <v>0.60231876373291</v>
+        <v>0.602318823337555</v>
       </c>
       <c r="H127" t="n">
         <v>12000</v>
@@ -4081,7 +4081,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G128" t="n">
-        <v>0.595949828624725</v>
+        <v>0.595949769020081</v>
       </c>
       <c r="H128" t="n">
         <v>34000</v>
@@ -4110,7 +4110,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G129" t="n">
-        <v>0.595949828624725</v>
+        <v>0.595949769020081</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>0.640532314777374</v>
+        <v>0.640532374382019</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4197,7 +4197,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G132" t="n">
-        <v>0.705131411552429</v>
+        <v>0.705131471157074</v>
       </c>
       <c r="H132" t="n">
         <v>19000</v>
@@ -4226,7 +4226,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G133" t="n">
-        <v>0.723328471183777</v>
+        <v>0.723328411579132</v>
       </c>
       <c r="H133" t="n">
         <v>9000</v>
@@ -4255,7 +4255,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H134" t="n">
         <v>96000</v>
@@ -4284,7 +4284,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G135" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G136" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H142" t="n">
         <v>3000</v>
@@ -4516,7 +4516,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G143" t="n">
-        <v>0.714230000972748</v>
+        <v>0.714229941368103</v>
       </c>
       <c r="H143" t="n">
         <v>46000</v>
@@ -4545,7 +4545,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G144" t="n">
-        <v>0.705131411552429</v>
+        <v>0.705131471157074</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4574,7 +4574,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G145" t="n">
-        <v>0.705131411552429</v>
+        <v>0.705131471157074</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709680736064911</v>
+        <v>0.709680676460266</v>
       </c>
       <c r="H146" t="n">
         <v>1000</v>
@@ -4632,7 +4632,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G147" t="n">
-        <v>0.709680736064911</v>
+        <v>0.709680676460266</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G148" t="n">
-        <v>0.675106525421143</v>
+        <v>0.675106465816498</v>
       </c>
       <c r="H148" t="n">
         <v>6000</v>
@@ -4690,7 +4690,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G149" t="n">
-        <v>0.684204995632172</v>
+        <v>0.684204936027527</v>
       </c>
       <c r="H149" t="n">
         <v>4000</v>
@@ -4719,7 +4719,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G150" t="n">
-        <v>0.684204995632172</v>
+        <v>0.684204936027527</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G151" t="n">
-        <v>0.693303525447845</v>
+        <v>0.693303465843201</v>
       </c>
       <c r="H151" t="n">
         <v>5000</v>
@@ -4777,7 +4777,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G152" t="n">
-        <v>0.693303525447845</v>
+        <v>0.693303465843201</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5009,7 +5009,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G160" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G165" t="n">
-        <v>0.576843023300171</v>
+        <v>0.576843082904816</v>
       </c>
       <c r="H165" t="n">
         <v>93000</v>
@@ -5589,7 +5589,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G180" t="n">
-        <v>0.522252202033997</v>
+        <v>0.522252261638641</v>
       </c>
       <c r="H180" t="n">
         <v>32000</v>
@@ -5618,7 +5618,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G181" t="n">
-        <v>0.53135073184967</v>
+        <v>0.531350672245026</v>
       </c>
       <c r="H181" t="n">
         <v>4000</v>
@@ -5647,7 +5647,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G182" t="n">
-        <v>0.53135073184967</v>
+        <v>0.531350672245026</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G191" t="n">
-        <v>0.471300780773163</v>
+        <v>0.471300810575485</v>
       </c>
       <c r="H191" t="n">
         <v>49000</v>
@@ -5937,7 +5937,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G192" t="n">
-        <v>0.493137151002884</v>
+        <v>0.493137121200562</v>
       </c>
       <c r="H192" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>0.49677649140358</v>
+        <v>0.496776521205902</v>
       </c>
       <c r="H193" t="n">
         <v>6000</v>
@@ -5995,7 +5995,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>0.49677649140358</v>
+        <v>0.496776521205902</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G201" t="n">
-        <v>0.491317451000214</v>
+        <v>0.491317421197891</v>
       </c>
       <c r="H201" t="n">
         <v>22000</v>
@@ -6227,7 +6227,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G202" t="n">
-        <v>0.491317451000214</v>
+        <v>0.491317421197891</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G210" t="n">
-        <v>0.356660038232803</v>
+        <v>0.356660068035126</v>
       </c>
       <c r="H210" t="n">
         <v>120000</v>
@@ -6546,7 +6546,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G213" t="n">
-        <v>0.516793191432953</v>
+        <v>0.516793131828308</v>
       </c>
       <c r="H213" t="n">
         <v>911000</v>
@@ -6749,7 +6749,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G220" t="n">
-        <v>0.658729314804077</v>
+        <v>0.658729255199432</v>
       </c>
       <c r="H220" t="n">
         <v>1878000</v>
@@ -6836,7 +6836,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G223" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H223" t="n">
         <v>4151000</v>
@@ -6923,7 +6923,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H226" t="n">
         <v>434000</v>
@@ -6952,7 +6952,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>0.67328679561615</v>
+        <v>0.673286855220795</v>
       </c>
       <c r="H227" t="n">
         <v>236000</v>
@@ -7126,7 +7126,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G233" t="n">
-        <v>0.753353357315063</v>
+        <v>0.753353416919708</v>
       </c>
       <c r="H233" t="n">
         <v>912000</v>
@@ -7329,7 +7329,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G240" t="n">
-        <v>0.68966406583786</v>
+        <v>0.689664125442505</v>
       </c>
       <c r="H240" t="n">
         <v>121000</v>
@@ -7677,7 +7677,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G252" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H252" t="n">
         <v>40000</v>
@@ -7706,7 +7706,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G253" t="n">
-        <v>0.749713957309723</v>
+        <v>0.749714016914368</v>
       </c>
       <c r="H253" t="n">
         <v>24000</v>
@@ -7822,7 +7822,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G257" t="n">
-        <v>0.68966406583786</v>
+        <v>0.689664125442505</v>
       </c>
       <c r="H257" t="n">
         <v>15000</v>
@@ -7851,7 +7851,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G258" t="n">
-        <v>0.68602466583252</v>
+        <v>0.686024725437164</v>
       </c>
       <c r="H258" t="n">
         <v>24000</v>
@@ -7880,7 +7880,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>0.67328679561615</v>
+        <v>0.673286855220795</v>
       </c>
       <c r="H259" t="n">
         <v>18000</v>
@@ -8054,7 +8054,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G265" t="n">
-        <v>0.68602466583252</v>
+        <v>0.686024725437164</v>
       </c>
       <c r="H265" t="n">
         <v>29000</v>
@@ -8141,7 +8141,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G268" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H268" t="n">
         <v>992000</v>
@@ -8344,7 +8344,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G275" t="n">
-        <v>0.74789434671402</v>
+        <v>0.747894287109375</v>
       </c>
       <c r="H275" t="n">
         <v>190000</v>
@@ -8518,7 +8518,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>0.978085696697235</v>
+        <v>0.97808563709259</v>
       </c>
       <c r="H281" t="n">
         <v>1188000</v>
@@ -8547,7 +8547,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G282" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H282" t="n">
         <v>952000</v>
@@ -8605,7 +8605,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G284" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H284" t="n">
         <v>356000</v>
@@ -8634,7 +8634,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H285" t="n">
         <v>1039000</v>
@@ -8721,7 +8721,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G288" t="n">
-        <v>1.41026282310486</v>
+        <v>1.41026294231415</v>
       </c>
       <c r="H288" t="n">
         <v>1203000</v>
@@ -8750,7 +8750,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>1.3465735912323</v>
+        <v>1.34657371044159</v>
       </c>
       <c r="H289" t="n">
         <v>817000</v>
@@ -8924,7 +8924,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H295" t="n">
         <v>209000</v>
@@ -8982,7 +8982,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G297" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H297" t="n">
         <v>294000</v>
@@ -9127,7 +9127,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H302" t="n">
         <v>179000</v>
@@ -9156,7 +9156,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H303" t="n">
         <v>169000</v>
@@ -9243,7 +9243,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G306" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H306" t="n">
         <v>84000</v>
@@ -9272,7 +9272,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H307" t="n">
         <v>56000</v>
@@ -9359,7 +9359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H310" t="n">
         <v>43000</v>
@@ -9475,7 +9475,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H314" t="n">
         <v>31000</v>
@@ -9504,7 +9504,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H315" t="n">
         <v>10000</v>
@@ -9562,7 +9562,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H317" t="n">
         <v>70000</v>
@@ -9620,7 +9620,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G319" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H319" t="n">
         <v>36000</v>
@@ -9678,7 +9678,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G321" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H321" t="n">
         <v>22000</v>
@@ -9765,7 +9765,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G324" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H324" t="n">
         <v>16000</v>
@@ -9852,7 +9852,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G327" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H327" t="n">
         <v>195000</v>
@@ -9968,7 +9968,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>1.12821042537689</v>
+        <v>1.1282103061676</v>
       </c>
       <c r="H331" t="n">
         <v>17000</v>
@@ -10026,7 +10026,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G333" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H333" t="n">
         <v>60000</v>
@@ -10171,7 +10171,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G338" t="n">
-        <v>1.12821042537689</v>
+        <v>1.1282103061676</v>
       </c>
       <c r="H338" t="n">
         <v>16000</v>
@@ -10287,7 +10287,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G342" t="n">
-        <v>1.12821042537689</v>
+        <v>1.1282103061676</v>
       </c>
       <c r="H342" t="n">
         <v>27000</v>
@@ -10606,7 +10606,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G353" t="n">
-        <v>0.978085696697235</v>
+        <v>0.97808563709259</v>
       </c>
       <c r="H353" t="n">
         <v>35000</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H354" t="n">
         <v>49000</v>
@@ -10693,7 +10693,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H356" t="n">
         <v>25000</v>
@@ -10780,7 +10780,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06452107429504</v>
+        <v>1.06452095508575</v>
       </c>
       <c r="H359" t="n">
         <v>64000</v>
@@ -10809,7 +10809,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H360" t="n">
         <v>16000</v>
@@ -10867,7 +10867,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G362" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H362" t="n">
         <v>17000</v>
@@ -10896,7 +10896,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G363" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H363" t="n">
         <v>16000</v>
@@ -10925,7 +10925,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G364" t="n">
-        <v>1.03267633914948</v>
+        <v>1.03267645835876</v>
       </c>
       <c r="H364" t="n">
         <v>36000</v>
@@ -10954,7 +10954,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G365" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H365" t="n">
         <v>5000</v>
@@ -11012,7 +11012,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G367" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H367" t="n">
         <v>47000</v>
@@ -11070,7 +11070,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G369" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H369" t="n">
         <v>16000</v>
@@ -11099,7 +11099,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H370" t="n">
         <v>393000</v>
@@ -11157,7 +11157,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>1.13275957107544</v>
+        <v>1.13275969028473</v>
       </c>
       <c r="H372" t="n">
         <v>87000</v>
@@ -11186,7 +11186,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>1.10091507434845</v>
+        <v>1.10091495513916</v>
       </c>
       <c r="H373" t="n">
         <v>90000</v>
@@ -11215,7 +11215,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09636569023132</v>
+        <v>1.09636580944061</v>
       </c>
       <c r="H374" t="n">
         <v>40000</v>
@@ -11302,7 +11302,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H377" t="n">
         <v>36000</v>
@@ -11331,7 +11331,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H378" t="n">
         <v>22000</v>
@@ -11418,7 +11418,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G381" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H381" t="n">
         <v>32000</v>
@@ -11505,7 +11505,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G384" t="n">
-        <v>1.06907021999359</v>
+        <v>1.06907033920288</v>
       </c>
       <c r="H384" t="n">
         <v>3000</v>
@@ -11621,7 +11621,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.04177498817444</v>
+        <v>1.04177486896515</v>
       </c>
       <c r="H388" t="n">
         <v>24000</v>
@@ -11650,7 +11650,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G389" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H389" t="n">
         <v>14000</v>
@@ -11679,7 +11679,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G390" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11737,7 +11737,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H392" t="n">
         <v>15000</v>
@@ -11795,7 +11795,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G394" t="n">
-        <v>0.991733372211456</v>
+        <v>0.991733312606812</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G395" t="n">
-        <v>0.878912270069122</v>
+        <v>0.878912329673767</v>
       </c>
       <c r="H395" t="n">
         <v>96000</v>
@@ -11853,7 +11853,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G396" t="n">
-        <v>0.83887904882431</v>
+        <v>0.838878989219666</v>
       </c>
       <c r="H396" t="n">
         <v>77000</v>
@@ -11940,7 +11940,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>0.978085696697235</v>
+        <v>0.97808563709259</v>
       </c>
       <c r="H399" t="n">
         <v>136000</v>
@@ -12201,7 +12201,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G408" t="n">
-        <v>0.645991444587708</v>
+        <v>0.645991384983063</v>
       </c>
       <c r="H408" t="n">
         <v>19000</v>
@@ -12317,7 +12317,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H412" t="n">
         <v>150000</v>
@@ -12462,7 +12462,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G417" t="n">
-        <v>0.707861065864563</v>
+        <v>0.707861006259918</v>
       </c>
       <c r="H417" t="n">
         <v>29000</v>
@@ -12491,7 +12491,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H418" t="n">
         <v>54000</v>
@@ -12636,7 +12636,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G423" t="n">
-        <v>0.751533627510071</v>
+        <v>0.751533687114716</v>
       </c>
       <c r="H423" t="n">
         <v>21000</v>
@@ -12694,7 +12694,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G425" t="n">
-        <v>0.756992816925049</v>
+        <v>0.756992757320404</v>
       </c>
       <c r="H425" t="n">
         <v>26000</v>
@@ -12984,7 +12984,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G435" t="n">
-        <v>0.901658415794373</v>
+        <v>0.901658475399017</v>
       </c>
       <c r="H435" t="n">
         <v>91000</v>
@@ -13013,7 +13013,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G436" t="n">
-        <v>0.922585010528564</v>
+        <v>0.92258495092392</v>
       </c>
       <c r="H436" t="n">
         <v>16000</v>
@@ -13100,7 +13100,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G439" t="n">
-        <v>0.890740275382996</v>
+        <v>0.890740215778351</v>
       </c>
       <c r="H439" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G443" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H443" t="n">
         <v>41000</v>
@@ -13361,7 +13361,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G448" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H448" t="n">
         <v>206000</v>
@@ -13622,7 +13622,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G457" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H457" t="n">
         <v>32000</v>
@@ -13680,7 +13680,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G459" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H459" t="n">
         <v>25000</v>
@@ -13767,7 +13767,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G462" t="n">
-        <v>1.06452107429504</v>
+        <v>1.06452095508575</v>
       </c>
       <c r="H462" t="n">
         <v>81000</v>
@@ -14057,7 +14057,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G472" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H472" t="n">
         <v>34000</v>
@@ -14086,7 +14086,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G473" t="n">
-        <v>1.06452107429504</v>
+        <v>1.06452095508575</v>
       </c>
       <c r="H473" t="n">
         <v>40000</v>
@@ -14144,7 +14144,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>1.04450440406799</v>
+        <v>1.04450452327728</v>
       </c>
       <c r="H475" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G481" t="n">
-        <v>0.993552982807159</v>
+        <v>0.993553042411804</v>
       </c>
       <c r="H481" t="n">
         <v>24000</v>
@@ -14347,7 +14347,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G482" t="n">
-        <v>1.04450440406799</v>
+        <v>1.04450452327728</v>
       </c>
       <c r="H482" t="n">
         <v>61000</v>
@@ -14405,7 +14405,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G484" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H484" t="n">
         <v>17000</v>
@@ -14492,7 +14492,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H487" t="n">
         <v>7000</v>
@@ -14521,7 +14521,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G488" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H488" t="n">
         <v>20000</v>
@@ -14550,7 +14550,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G489" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H489" t="n">
         <v>10000</v>
@@ -14753,7 +14753,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G496" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H496" t="n">
         <v>5000</v>
@@ -14811,7 +14811,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G498" t="n">
-        <v>1.02266800403595</v>
+        <v>1.02266812324524</v>
       </c>
       <c r="H498" t="n">
         <v>11000</v>
@@ -14869,7 +14869,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G500" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H500" t="n">
         <v>10000</v>
@@ -14956,7 +14956,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G503" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H503" t="n">
         <v>18000</v>
@@ -14985,7 +14985,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>0.933503091335297</v>
+        <v>0.933503150939941</v>
       </c>
       <c r="H504" t="n">
         <v>14000</v>
@@ -15014,7 +15014,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G505" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H505" t="n">
         <v>14000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G506" t="n">
-        <v>0.949880361557007</v>
+        <v>0.949880421161652</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15188,7 +15188,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G511" t="n">
-        <v>0.968077301979065</v>
+        <v>0.96807736158371</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15333,7 +15333,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>0.942601561546326</v>
+        <v>0.94260162115097</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>0.955339372158051</v>
+        <v>0.955339312553406</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>0.955339372158051</v>
+        <v>0.955339312553406</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G520" t="n">
-        <v>0.951700091362</v>
+        <v>0.951700031757355</v>
       </c>
       <c r="H520" t="n">
         <v>26000</v>
@@ -15507,7 +15507,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G522" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H522" t="n">
         <v>4000</v>
@@ -15565,7 +15565,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G524" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15623,7 +15623,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G526" t="n">
-        <v>0.949880361557007</v>
+        <v>0.949880421161652</v>
       </c>
       <c r="H526" t="n">
         <v>9000</v>
@@ -15710,7 +15710,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G529" t="n">
-        <v>0.922585010528564</v>
+        <v>0.92258495092392</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G530" t="n">
-        <v>0.933503091335297</v>
+        <v>0.933503150939941</v>
       </c>
       <c r="H530" t="n">
         <v>15000</v>
@@ -15768,7 +15768,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G531" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H531" t="n">
         <v>4000</v>
@@ -15797,7 +15797,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>0.942601561546326</v>
+        <v>0.94260162115097</v>
       </c>
       <c r="H532" t="n">
         <v>11000</v>
@@ -15826,7 +15826,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>0.933503091335297</v>
+        <v>0.933503150939941</v>
       </c>
       <c r="H533" t="n">
         <v>4000</v>
@@ -15855,7 +15855,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G534" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H534" t="n">
         <v>11000</v>
@@ -15884,7 +15884,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G535" t="n">
-        <v>0.922585010528564</v>
+        <v>0.92258495092392</v>
       </c>
       <c r="H535" t="n">
         <v>4000</v>
@@ -15942,7 +15942,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G537" t="n">
-        <v>0.878912270069122</v>
+        <v>0.878912329673767</v>
       </c>
       <c r="H537" t="n">
         <v>25000</v>
@@ -15971,7 +15971,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G538" t="n">
-        <v>0.929863631725311</v>
+        <v>0.929863691329956</v>
       </c>
       <c r="H538" t="n">
         <v>48000</v>
@@ -16029,7 +16029,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G540" t="n">
-        <v>0.917125821113586</v>
+        <v>0.917125880718231</v>
       </c>
       <c r="H540" t="n">
         <v>1000</v>
@@ -16232,7 +16232,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G547" t="n">
-        <v>0.908937275409698</v>
+        <v>0.908937215805054</v>
       </c>
       <c r="H547" t="n">
         <v>16000</v>
@@ -16348,7 +16348,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G551" t="n">
-        <v>0.875272929668427</v>
+        <v>0.875272870063782</v>
       </c>
       <c r="H551" t="n">
         <v>4000</v>
@@ -16551,7 +16551,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G558" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H558" t="n">
         <v>137000</v>
@@ -16580,7 +16580,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G559" t="n">
-        <v>0.986274302005768</v>
+        <v>0.986274242401123</v>
       </c>
       <c r="H559" t="n">
         <v>23000</v>
@@ -16754,7 +16754,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G565" t="n">
-        <v>0.942601561546326</v>
+        <v>0.94260162115097</v>
       </c>
       <c r="H565" t="n">
         <v>49000</v>
@@ -16783,7 +16783,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G566" t="n">
-        <v>0.980815052986145</v>
+        <v>0.98081511259079</v>
       </c>
       <c r="H566" t="n">
         <v>25000</v>
@@ -16841,7 +16841,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G568" t="n">
-        <v>0.944421231746674</v>
+        <v>0.944421291351318</v>
       </c>
       <c r="H568" t="n">
         <v>6000</v>
@@ -16928,7 +16928,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G571" t="n">
-        <v>1.25012981891632</v>
+        <v>1.25012993812561</v>
       </c>
       <c r="H571" t="n">
         <v>328000</v>
@@ -17015,7 +17015,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G574" t="n">
-        <v>1.30835998058319</v>
+        <v>1.30836009979248</v>
       </c>
       <c r="H574" t="n">
         <v>231000</v>
@@ -17044,7 +17044,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G575" t="n">
-        <v>1.56675660610199</v>
+        <v>1.56675672531128</v>
       </c>
       <c r="H575" t="n">
         <v>931000</v>
@@ -17102,7 +17102,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>1.97436833381653</v>
+        <v>1.97436821460724</v>
       </c>
       <c r="H577" t="n">
         <v>1358000</v>
@@ -17160,7 +17160,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G579" t="n">
-        <v>1.76146388053894</v>
+        <v>1.76146399974823</v>
       </c>
       <c r="H579" t="n">
         <v>906000</v>
@@ -17189,7 +17189,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G580" t="n">
-        <v>1.77238214015961</v>
+        <v>1.77238202095032</v>
       </c>
       <c r="H580" t="n">
         <v>765000</v>
@@ -17363,7 +17363,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.21547746658325</v>
+        <v>2.21547770500183</v>
       </c>
       <c r="H586" t="n">
         <v>495000</v>
@@ -17392,7 +17392,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.63400721549988</v>
+        <v>2.63400745391846</v>
       </c>
       <c r="H587" t="n">
         <v>835000</v>
@@ -17479,7 +17479,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>2.67040109634399</v>
+        <v>2.67040133476257</v>
       </c>
       <c r="H590" t="n">
         <v>876000</v>
@@ -17566,7 +17566,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G593" t="n">
-        <v>2.83872294425964</v>
+        <v>2.83872270584106</v>
       </c>
       <c r="H593" t="n">
         <v>439000</v>
@@ -17595,7 +17595,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G594" t="n">
-        <v>2.90696144104004</v>
+        <v>2.90696120262146</v>
       </c>
       <c r="H594" t="n">
         <v>251000</v>
@@ -17624,7 +17624,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G595" t="n">
-        <v>2.9706506729126</v>
+        <v>2.97065091133118</v>
       </c>
       <c r="H595" t="n">
         <v>595000</v>
@@ -17740,7 +17740,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>2.76593518257141</v>
+        <v>2.76593494415283</v>
       </c>
       <c r="H599" t="n">
         <v>163000</v>
@@ -17885,7 +17885,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.76593518257141</v>
+        <v>2.76593494415283</v>
       </c>
       <c r="H604" t="n">
         <v>50000</v>
@@ -18001,7 +18001,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>2.52027630805969</v>
+        <v>2.52027654647827</v>
       </c>
       <c r="H608" t="n">
         <v>115000</v>
@@ -18059,7 +18059,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.71134448051453</v>
+        <v>2.71134424209595</v>
       </c>
       <c r="H610" t="n">
         <v>132000</v>
@@ -18117,7 +18117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>2.6931471824646</v>
+        <v>2.69314742088318</v>
       </c>
       <c r="H612" t="n">
         <v>78000</v>
@@ -18146,7 +18146,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.77503347396851</v>
+        <v>2.77503371238708</v>
       </c>
       <c r="H613" t="n">
         <v>162000</v>
@@ -18175,7 +18175,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.76593518257141</v>
+        <v>2.76593494415283</v>
       </c>
       <c r="H614" t="n">
         <v>174000</v>
@@ -18349,7 +18349,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G620" t="n">
-        <v>2.79323029518127</v>
+        <v>2.79323053359985</v>
       </c>
       <c r="H620" t="n">
         <v>99000</v>
@@ -18407,7 +18407,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.54385447502136</v>
+        <v>3.54385423660278</v>
       </c>
       <c r="H622" t="n">
         <v>833000</v>
@@ -18465,7 +18465,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>4.01242589950562</v>
+        <v>4.01242542266846</v>
       </c>
       <c r="H624" t="n">
         <v>972000</v>
@@ -18523,7 +18523,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>3.8213574886322</v>
+        <v>3.82135725021362</v>
       </c>
       <c r="H626" t="n">
         <v>371000</v>
@@ -18552,7 +18552,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>3.73492217063904</v>
+        <v>3.73492240905762</v>
       </c>
       <c r="H627" t="n">
         <v>215000</v>
@@ -18726,7 +18726,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>4.2489857673645</v>
+        <v>4.24898624420166</v>
       </c>
       <c r="H633" t="n">
         <v>78000</v>
@@ -18813,7 +18813,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>4.74030303955078</v>
+        <v>4.74030351638794</v>
       </c>
       <c r="H636" t="n">
         <v>826000</v>
@@ -18871,7 +18871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G638" t="n">
-        <v>5.64105129241943</v>
+        <v>5.64105176925659</v>
       </c>
       <c r="H638" t="n">
         <v>576000</v>
@@ -19132,7 +19132,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>5.84121799468994</v>
+        <v>5.8412184715271</v>
       </c>
       <c r="H647" t="n">
         <v>69000</v>
@@ -19277,7 +19277,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>6.19605827331543</v>
+        <v>6.19605875015259</v>
       </c>
       <c r="H652" t="n">
         <v>166000</v>
@@ -19422,7 +19422,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G657" t="n">
-        <v>6.19605827331543</v>
+        <v>6.19605875015259</v>
       </c>
       <c r="H657" t="n">
         <v>58500</v>
@@ -19538,7 +19538,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G661" t="n">
-        <v>6.28704357147217</v>
+        <v>6.28704309463501</v>
       </c>
       <c r="H661" t="n">
         <v>49000</v>
@@ -19741,7 +19741,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G668" t="n">
-        <v>6.34163427352905</v>
+        <v>6.34163379669189</v>
       </c>
       <c r="H668" t="n">
         <v>29500</v>
@@ -19770,7 +19770,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>6.45081567764282</v>
+        <v>6.45081615447998</v>
       </c>
       <c r="H669" t="n">
         <v>74500</v>
@@ -19828,7 +19828,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>6.34163427352905</v>
+        <v>6.34163379669189</v>
       </c>
       <c r="H671" t="n">
         <v>42500</v>
@@ -19886,7 +19886,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G673" t="n">
-        <v>6.31433868408203</v>
+        <v>6.31433916091919</v>
       </c>
       <c r="H673" t="n">
         <v>22500</v>
@@ -20031,7 +20031,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>5.8048243522644</v>
+        <v>5.80482482910156</v>
       </c>
       <c r="H678" t="n">
         <v>177429</v>
@@ -20147,7 +20147,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>5.55006694793701</v>
+        <v>5.55006742477417</v>
       </c>
       <c r="H682" t="n">
         <v>47228</v>
@@ -20292,7 +20292,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>6.05958127975464</v>
+        <v>6.0595817565918</v>
       </c>
       <c r="H687" t="n">
         <v>134241</v>
@@ -60782,6 +60782,35 @@
         <v>0</v>
       </c>
       <c r="I2083" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2084" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2084" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2084" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -60814,6 +60814,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2085">
+      <c r="A2085" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2085" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2085" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2085" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -60843,6 +60843,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2086">
+      <c r="A2086" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2086" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2086" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -543,7 +543,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989003837108612</v>
+        <v>0.989003777503967</v>
       </c>
       <c r="H6" t="n">
         <v>114000</v>
@@ -630,7 +630,7 @@
         <v>0.954100012779236</v>
       </c>
       <c r="G9" t="n">
-        <v>0.868085086345673</v>
+        <v>0.868085145950317</v>
       </c>
       <c r="H9" t="n">
         <v>39000</v>
@@ -659,7 +659,7 @@
         <v>0.981899976730347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.893378794193268</v>
+        <v>0.893378853797913</v>
       </c>
       <c r="H10" t="n">
         <v>23000</v>
@@ -1007,7 +1007,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G22" t="n">
-        <v>1.00902032852173</v>
+        <v>1.00902044773102</v>
       </c>
       <c r="H22" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H26" t="n">
         <v>1000</v>
@@ -1152,7 +1152,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G27" t="n">
-        <v>0.983908593654633</v>
+        <v>0.983908712863922</v>
       </c>
       <c r="H27" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G28" t="n">
-        <v>0.983908593654633</v>
+        <v>0.983908712863922</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G29" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H29" t="n">
         <v>34000</v>
@@ -1326,7 +1326,7 @@
         <v>1.08519995212555</v>
       </c>
       <c r="G33" t="n">
-        <v>0.987366020679474</v>
+        <v>0.987365961074829</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G35" t="n">
-        <v>1.02685332298279</v>
+        <v>1.02685344219208</v>
       </c>
       <c r="H35" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G36" t="n">
-        <v>1.02685332298279</v>
+        <v>1.02685344219208</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G37" t="n">
-        <v>1.02685332298279</v>
+        <v>1.02685344219208</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G39" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H39" t="n">
         <v>14000</v>
@@ -1529,7 +1529,7 @@
         <v>1.0654000043869</v>
       </c>
       <c r="G40" t="n">
-        <v>0.96935111284256</v>
+        <v>0.969351053237915</v>
       </c>
       <c r="H40" t="n">
         <v>5000</v>
@@ -1587,7 +1587,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G42" t="n">
-        <v>0.98081511259079</v>
+        <v>0.980815052986145</v>
       </c>
       <c r="H42" t="n">
         <v>55000</v>
@@ -1616,7 +1616,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>0.907117486000061</v>
+        <v>0.907117545604706</v>
       </c>
       <c r="H43" t="n">
         <v>60000</v>
@@ -2138,7 +2138,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G61" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H61" t="n">
         <v>3000</v>
@@ -2660,7 +2660,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>0.826141119003296</v>
+        <v>0.826141178607941</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G80" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H80" t="n">
         <v>21000</v>
@@ -2718,7 +2718,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G81" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G82" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2776,7 +2776,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G83" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>0.802500009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>0.730152308940887</v>
+        <v>0.730152249336243</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G91" t="n">
-        <v>0.713320136070251</v>
+        <v>0.713320076465607</v>
       </c>
       <c r="H91" t="n">
         <v>11000</v>
@@ -3037,7 +3037,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G92" t="n">
-        <v>0.689664125442505</v>
+        <v>0.68966406583786</v>
       </c>
       <c r="H92" t="n">
         <v>36000</v>
@@ -3066,7 +3066,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G93" t="n">
-        <v>0.707861006259918</v>
+        <v>0.707861065864563</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>0.673286855220795</v>
+        <v>0.67328679561615</v>
       </c>
       <c r="H95" t="n">
         <v>2000</v>
@@ -3269,7 +3269,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G100" t="n">
-        <v>0.693303465843201</v>
+        <v>0.693303525447845</v>
       </c>
       <c r="H100" t="n">
         <v>2000</v>
@@ -3298,7 +3298,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G101" t="n">
-        <v>0.704221665859222</v>
+        <v>0.704221606254578</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G102" t="n">
-        <v>0.704221665859222</v>
+        <v>0.704221606254578</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G103" t="n">
-        <v>0.704221665859222</v>
+        <v>0.704221606254578</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G111" t="n">
-        <v>0.580027520656586</v>
+        <v>0.580027461051941</v>
       </c>
       <c r="H111" t="n">
         <v>17000</v>
@@ -3675,7 +3675,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G114" t="n">
-        <v>0.576843082904816</v>
+        <v>0.576843023300171</v>
       </c>
       <c r="H114" t="n">
         <v>3000</v>
@@ -3733,7 +3733,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>0.564105153083801</v>
+        <v>0.564105212688446</v>
       </c>
       <c r="H116" t="n">
         <v>3000</v>
@@ -3820,7 +3820,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G119" t="n">
-        <v>0.624155104160309</v>
+        <v>0.624155044555664</v>
       </c>
       <c r="H119" t="n">
         <v>58000</v>
@@ -3878,7 +3878,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G121" t="n">
-        <v>0.618695974349976</v>
+        <v>0.61869603395462</v>
       </c>
       <c r="H121" t="n">
         <v>8000</v>
@@ -3965,7 +3965,7 @@
         <v>0.676999986171722</v>
       </c>
       <c r="G124" t="n">
-        <v>0.615966498851776</v>
+        <v>0.615966439247131</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G125" t="n">
-        <v>0.595039963722229</v>
+        <v>0.595040023326874</v>
       </c>
       <c r="H125" t="n">
         <v>5000</v>
@@ -4052,7 +4052,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G127" t="n">
-        <v>0.602318823337555</v>
+        <v>0.60231876373291</v>
       </c>
       <c r="H127" t="n">
         <v>12000</v>
@@ -4081,7 +4081,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G128" t="n">
-        <v>0.595949769020081</v>
+        <v>0.595949828624725</v>
       </c>
       <c r="H128" t="n">
         <v>34000</v>
@@ -4110,7 +4110,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G129" t="n">
-        <v>0.595949769020081</v>
+        <v>0.595949828624725</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>0.640532374382019</v>
+        <v>0.640532314777374</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4197,7 +4197,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G132" t="n">
-        <v>0.705131471157074</v>
+        <v>0.705131411552429</v>
       </c>
       <c r="H132" t="n">
         <v>19000</v>
@@ -4226,7 +4226,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G133" t="n">
-        <v>0.723328411579132</v>
+        <v>0.723328471183777</v>
       </c>
       <c r="H133" t="n">
         <v>9000</v>
@@ -4255,7 +4255,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H134" t="n">
         <v>96000</v>
@@ -4284,7 +4284,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G135" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G136" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H142" t="n">
         <v>3000</v>
@@ -4516,7 +4516,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G143" t="n">
-        <v>0.714229941368103</v>
+        <v>0.714230000972748</v>
       </c>
       <c r="H143" t="n">
         <v>46000</v>
@@ -4545,7 +4545,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G144" t="n">
-        <v>0.705131471157074</v>
+        <v>0.705131411552429</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4574,7 +4574,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G145" t="n">
-        <v>0.705131471157074</v>
+        <v>0.705131411552429</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709680676460266</v>
+        <v>0.709680736064911</v>
       </c>
       <c r="H146" t="n">
         <v>1000</v>
@@ -4632,7 +4632,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G147" t="n">
-        <v>0.709680676460266</v>
+        <v>0.709680736064911</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G148" t="n">
-        <v>0.675106465816498</v>
+        <v>0.675106525421143</v>
       </c>
       <c r="H148" t="n">
         <v>6000</v>
@@ -4690,7 +4690,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G149" t="n">
-        <v>0.684204936027527</v>
+        <v>0.684204995632172</v>
       </c>
       <c r="H149" t="n">
         <v>4000</v>
@@ -4719,7 +4719,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G150" t="n">
-        <v>0.684204936027527</v>
+        <v>0.684204995632172</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G151" t="n">
-        <v>0.693303465843201</v>
+        <v>0.693303525447845</v>
       </c>
       <c r="H151" t="n">
         <v>5000</v>
@@ -4777,7 +4777,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G152" t="n">
-        <v>0.693303465843201</v>
+        <v>0.693303525447845</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5009,7 +5009,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G160" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G165" t="n">
-        <v>0.576843082904816</v>
+        <v>0.576843023300171</v>
       </c>
       <c r="H165" t="n">
         <v>93000</v>
@@ -5589,7 +5589,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G180" t="n">
-        <v>0.522252261638641</v>
+        <v>0.522252202033997</v>
       </c>
       <c r="H180" t="n">
         <v>32000</v>
@@ -5618,7 +5618,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G181" t="n">
-        <v>0.531350672245026</v>
+        <v>0.53135073184967</v>
       </c>
       <c r="H181" t="n">
         <v>4000</v>
@@ -5647,7 +5647,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G182" t="n">
-        <v>0.531350672245026</v>
+        <v>0.53135073184967</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G191" t="n">
-        <v>0.471300810575485</v>
+        <v>0.471300780773163</v>
       </c>
       <c r="H191" t="n">
         <v>49000</v>
@@ -5937,7 +5937,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G192" t="n">
-        <v>0.493137121200562</v>
+        <v>0.493137151002884</v>
       </c>
       <c r="H192" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>0.496776521205902</v>
+        <v>0.49677649140358</v>
       </c>
       <c r="H193" t="n">
         <v>6000</v>
@@ -5995,7 +5995,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>0.496776521205902</v>
+        <v>0.49677649140358</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G201" t="n">
-        <v>0.491317421197891</v>
+        <v>0.491317451000214</v>
       </c>
       <c r="H201" t="n">
         <v>22000</v>
@@ -6227,7 +6227,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G202" t="n">
-        <v>0.491317421197891</v>
+        <v>0.491317451000214</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G210" t="n">
-        <v>0.356660068035126</v>
+        <v>0.356660038232803</v>
       </c>
       <c r="H210" t="n">
         <v>120000</v>
@@ -6546,7 +6546,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G213" t="n">
-        <v>0.516793131828308</v>
+        <v>0.516793191432953</v>
       </c>
       <c r="H213" t="n">
         <v>911000</v>
@@ -6749,7 +6749,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G220" t="n">
-        <v>0.658729255199432</v>
+        <v>0.658729314804077</v>
       </c>
       <c r="H220" t="n">
         <v>1878000</v>
@@ -6836,7 +6836,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G223" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H223" t="n">
         <v>4151000</v>
@@ -6923,7 +6923,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H226" t="n">
         <v>434000</v>
@@ -6952,7 +6952,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>0.673286855220795</v>
+        <v>0.67328679561615</v>
       </c>
       <c r="H227" t="n">
         <v>236000</v>
@@ -7126,7 +7126,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G233" t="n">
-        <v>0.753353416919708</v>
+        <v>0.753353357315063</v>
       </c>
       <c r="H233" t="n">
         <v>912000</v>
@@ -7329,7 +7329,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G240" t="n">
-        <v>0.689664125442505</v>
+        <v>0.68966406583786</v>
       </c>
       <c r="H240" t="n">
         <v>121000</v>
@@ -7677,7 +7677,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G252" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H252" t="n">
         <v>40000</v>
@@ -7706,7 +7706,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G253" t="n">
-        <v>0.749714016914368</v>
+        <v>0.749713957309723</v>
       </c>
       <c r="H253" t="n">
         <v>24000</v>
@@ -7822,7 +7822,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G257" t="n">
-        <v>0.689664125442505</v>
+        <v>0.68966406583786</v>
       </c>
       <c r="H257" t="n">
         <v>15000</v>
@@ -7851,7 +7851,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G258" t="n">
-        <v>0.686024725437164</v>
+        <v>0.68602466583252</v>
       </c>
       <c r="H258" t="n">
         <v>24000</v>
@@ -7880,7 +7880,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>0.673286855220795</v>
+        <v>0.67328679561615</v>
       </c>
       <c r="H259" t="n">
         <v>18000</v>
@@ -8054,7 +8054,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G265" t="n">
-        <v>0.686024725437164</v>
+        <v>0.68602466583252</v>
       </c>
       <c r="H265" t="n">
         <v>29000</v>
@@ -8141,7 +8141,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G268" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H268" t="n">
         <v>992000</v>
@@ -8344,7 +8344,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G275" t="n">
-        <v>0.747894287109375</v>
+        <v>0.74789434671402</v>
       </c>
       <c r="H275" t="n">
         <v>190000</v>
@@ -8518,7 +8518,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>0.97808563709259</v>
+        <v>0.978085696697235</v>
       </c>
       <c r="H281" t="n">
         <v>1188000</v>
@@ -8547,7 +8547,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G282" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H282" t="n">
         <v>952000</v>
@@ -8605,7 +8605,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G284" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H284" t="n">
         <v>356000</v>
@@ -8634,7 +8634,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H285" t="n">
         <v>1039000</v>
@@ -8721,7 +8721,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G288" t="n">
-        <v>1.41026294231415</v>
+        <v>1.41026282310486</v>
       </c>
       <c r="H288" t="n">
         <v>1203000</v>
@@ -8750,7 +8750,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>1.34657371044159</v>
+        <v>1.3465735912323</v>
       </c>
       <c r="H289" t="n">
         <v>817000</v>
@@ -8924,7 +8924,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H295" t="n">
         <v>209000</v>
@@ -8982,7 +8982,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G297" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H297" t="n">
         <v>294000</v>
@@ -9127,7 +9127,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H302" t="n">
         <v>179000</v>
@@ -9156,7 +9156,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H303" t="n">
         <v>169000</v>
@@ -9243,7 +9243,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G306" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H306" t="n">
         <v>84000</v>
@@ -9272,7 +9272,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H307" t="n">
         <v>56000</v>
@@ -9359,7 +9359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H310" t="n">
         <v>43000</v>
@@ -9475,7 +9475,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H314" t="n">
         <v>31000</v>
@@ -9504,7 +9504,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H315" t="n">
         <v>10000</v>
@@ -9562,7 +9562,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H317" t="n">
         <v>70000</v>
@@ -9620,7 +9620,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G319" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H319" t="n">
         <v>36000</v>
@@ -9678,7 +9678,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G321" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H321" t="n">
         <v>22000</v>
@@ -9765,7 +9765,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G324" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H324" t="n">
         <v>16000</v>
@@ -9852,7 +9852,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G327" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H327" t="n">
         <v>195000</v>
@@ -9968,7 +9968,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>1.1282103061676</v>
+        <v>1.12821042537689</v>
       </c>
       <c r="H331" t="n">
         <v>17000</v>
@@ -10026,7 +10026,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G333" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H333" t="n">
         <v>60000</v>
@@ -10171,7 +10171,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G338" t="n">
-        <v>1.1282103061676</v>
+        <v>1.12821042537689</v>
       </c>
       <c r="H338" t="n">
         <v>16000</v>
@@ -10287,7 +10287,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G342" t="n">
-        <v>1.1282103061676</v>
+        <v>1.12821042537689</v>
       </c>
       <c r="H342" t="n">
         <v>27000</v>
@@ -10606,7 +10606,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G353" t="n">
-        <v>0.97808563709259</v>
+        <v>0.978085696697235</v>
       </c>
       <c r="H353" t="n">
         <v>35000</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H354" t="n">
         <v>49000</v>
@@ -10693,7 +10693,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H356" t="n">
         <v>25000</v>
@@ -10780,7 +10780,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06452095508575</v>
+        <v>1.06452107429504</v>
       </c>
       <c r="H359" t="n">
         <v>64000</v>
@@ -10809,7 +10809,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H360" t="n">
         <v>16000</v>
@@ -10867,7 +10867,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G362" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H362" t="n">
         <v>17000</v>
@@ -10896,7 +10896,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G363" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H363" t="n">
         <v>16000</v>
@@ -10925,7 +10925,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G364" t="n">
-        <v>1.03267645835876</v>
+        <v>1.03267633914948</v>
       </c>
       <c r="H364" t="n">
         <v>36000</v>
@@ -10954,7 +10954,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G365" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H365" t="n">
         <v>5000</v>
@@ -11012,7 +11012,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G367" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H367" t="n">
         <v>47000</v>
@@ -11070,7 +11070,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G369" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H369" t="n">
         <v>16000</v>
@@ -11099,7 +11099,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H370" t="n">
         <v>393000</v>
@@ -11157,7 +11157,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>1.13275969028473</v>
+        <v>1.13275957107544</v>
       </c>
       <c r="H372" t="n">
         <v>87000</v>
@@ -11186,7 +11186,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>1.10091495513916</v>
+        <v>1.10091507434845</v>
       </c>
       <c r="H373" t="n">
         <v>90000</v>
@@ -11215,7 +11215,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09636580944061</v>
+        <v>1.09636569023132</v>
       </c>
       <c r="H374" t="n">
         <v>40000</v>
@@ -11302,7 +11302,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H377" t="n">
         <v>36000</v>
@@ -11331,7 +11331,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H378" t="n">
         <v>22000</v>
@@ -11418,7 +11418,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G381" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H381" t="n">
         <v>32000</v>
@@ -11505,7 +11505,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G384" t="n">
-        <v>1.06907033920288</v>
+        <v>1.06907021999359</v>
       </c>
       <c r="H384" t="n">
         <v>3000</v>
@@ -11621,7 +11621,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.04177486896515</v>
+        <v>1.04177498817444</v>
       </c>
       <c r="H388" t="n">
         <v>24000</v>
@@ -11650,7 +11650,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G389" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H389" t="n">
         <v>14000</v>
@@ -11679,7 +11679,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G390" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11737,7 +11737,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H392" t="n">
         <v>15000</v>
@@ -11795,7 +11795,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G394" t="n">
-        <v>0.991733312606812</v>
+        <v>0.991733372211456</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G395" t="n">
-        <v>0.878912329673767</v>
+        <v>0.878912270069122</v>
       </c>
       <c r="H395" t="n">
         <v>96000</v>
@@ -11853,7 +11853,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G396" t="n">
-        <v>0.838878989219666</v>
+        <v>0.83887904882431</v>
       </c>
       <c r="H396" t="n">
         <v>77000</v>
@@ -11940,7 +11940,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>0.97808563709259</v>
+        <v>0.978085696697235</v>
       </c>
       <c r="H399" t="n">
         <v>136000</v>
@@ -12201,7 +12201,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G408" t="n">
-        <v>0.645991384983063</v>
+        <v>0.645991444587708</v>
       </c>
       <c r="H408" t="n">
         <v>19000</v>
@@ -12317,7 +12317,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H412" t="n">
         <v>150000</v>
@@ -12462,7 +12462,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G417" t="n">
-        <v>0.707861006259918</v>
+        <v>0.707861065864563</v>
       </c>
       <c r="H417" t="n">
         <v>29000</v>
@@ -12491,7 +12491,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H418" t="n">
         <v>54000</v>
@@ -12636,7 +12636,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G423" t="n">
-        <v>0.751533687114716</v>
+        <v>0.751533627510071</v>
       </c>
       <c r="H423" t="n">
         <v>21000</v>
@@ -12694,7 +12694,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G425" t="n">
-        <v>0.756992757320404</v>
+        <v>0.756992816925049</v>
       </c>
       <c r="H425" t="n">
         <v>26000</v>
@@ -12984,7 +12984,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G435" t="n">
-        <v>0.901658475399017</v>
+        <v>0.901658415794373</v>
       </c>
       <c r="H435" t="n">
         <v>91000</v>
@@ -13013,7 +13013,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G436" t="n">
-        <v>0.92258495092392</v>
+        <v>0.922585010528564</v>
       </c>
       <c r="H436" t="n">
         <v>16000</v>
@@ -13100,7 +13100,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G439" t="n">
-        <v>0.890740215778351</v>
+        <v>0.890740275382996</v>
       </c>
       <c r="H439" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G443" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H443" t="n">
         <v>41000</v>
@@ -13361,7 +13361,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G448" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H448" t="n">
         <v>206000</v>
@@ -13622,7 +13622,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G457" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H457" t="n">
         <v>32000</v>
@@ -13680,7 +13680,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G459" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H459" t="n">
         <v>25000</v>
@@ -13767,7 +13767,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G462" t="n">
-        <v>1.06452095508575</v>
+        <v>1.06452107429504</v>
       </c>
       <c r="H462" t="n">
         <v>81000</v>
@@ -14057,7 +14057,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G472" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H472" t="n">
         <v>34000</v>
@@ -14086,7 +14086,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G473" t="n">
-        <v>1.06452095508575</v>
+        <v>1.06452107429504</v>
       </c>
       <c r="H473" t="n">
         <v>40000</v>
@@ -14144,7 +14144,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>1.04450452327728</v>
+        <v>1.04450440406799</v>
       </c>
       <c r="H475" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G481" t="n">
-        <v>0.993553042411804</v>
+        <v>0.993552982807159</v>
       </c>
       <c r="H481" t="n">
         <v>24000</v>
@@ -14347,7 +14347,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G482" t="n">
-        <v>1.04450452327728</v>
+        <v>1.04450440406799</v>
       </c>
       <c r="H482" t="n">
         <v>61000</v>
@@ -14405,7 +14405,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G484" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H484" t="n">
         <v>17000</v>
@@ -14492,7 +14492,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H487" t="n">
         <v>7000</v>
@@ -14521,7 +14521,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G488" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H488" t="n">
         <v>20000</v>
@@ -14550,7 +14550,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G489" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H489" t="n">
         <v>10000</v>
@@ -14753,7 +14753,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H496" t="n">
         <v>5000</v>
@@ -14811,7 +14811,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G498" t="n">
-        <v>1.02266812324524</v>
+        <v>1.02266800403595</v>
       </c>
       <c r="H498" t="n">
         <v>11000</v>
@@ -14869,7 +14869,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G500" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H500" t="n">
         <v>10000</v>
@@ -14956,7 +14956,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G503" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H503" t="n">
         <v>18000</v>
@@ -14985,7 +14985,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>0.933503150939941</v>
+        <v>0.933503091335297</v>
       </c>
       <c r="H504" t="n">
         <v>14000</v>
@@ -15014,7 +15014,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G505" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H505" t="n">
         <v>14000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G506" t="n">
-        <v>0.949880421161652</v>
+        <v>0.949880361557007</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15188,7 +15188,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G511" t="n">
-        <v>0.96807736158371</v>
+        <v>0.968077301979065</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15333,7 +15333,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>0.94260162115097</v>
+        <v>0.942601561546326</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>0.955339312553406</v>
+        <v>0.955339372158051</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>0.955339312553406</v>
+        <v>0.955339372158051</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G520" t="n">
-        <v>0.951700031757355</v>
+        <v>0.951700091362</v>
       </c>
       <c r="H520" t="n">
         <v>26000</v>
@@ -15507,7 +15507,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G522" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H522" t="n">
         <v>4000</v>
@@ -15565,7 +15565,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G524" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15623,7 +15623,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G526" t="n">
-        <v>0.949880421161652</v>
+        <v>0.949880361557007</v>
       </c>
       <c r="H526" t="n">
         <v>9000</v>
@@ -15710,7 +15710,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G529" t="n">
-        <v>0.92258495092392</v>
+        <v>0.922585010528564</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G530" t="n">
-        <v>0.933503150939941</v>
+        <v>0.933503091335297</v>
       </c>
       <c r="H530" t="n">
         <v>15000</v>
@@ -15768,7 +15768,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G531" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H531" t="n">
         <v>4000</v>
@@ -15797,7 +15797,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>0.94260162115097</v>
+        <v>0.942601561546326</v>
       </c>
       <c r="H532" t="n">
         <v>11000</v>
@@ -15826,7 +15826,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>0.933503150939941</v>
+        <v>0.933503091335297</v>
       </c>
       <c r="H533" t="n">
         <v>4000</v>
@@ -15855,7 +15855,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G534" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H534" t="n">
         <v>11000</v>
@@ -15884,7 +15884,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G535" t="n">
-        <v>0.92258495092392</v>
+        <v>0.922585010528564</v>
       </c>
       <c r="H535" t="n">
         <v>4000</v>
@@ -15942,7 +15942,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G537" t="n">
-        <v>0.878912329673767</v>
+        <v>0.878912270069122</v>
       </c>
       <c r="H537" t="n">
         <v>25000</v>
@@ -15971,7 +15971,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G538" t="n">
-        <v>0.929863691329956</v>
+        <v>0.929863631725311</v>
       </c>
       <c r="H538" t="n">
         <v>48000</v>
@@ -16029,7 +16029,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G540" t="n">
-        <v>0.917125880718231</v>
+        <v>0.917125821113586</v>
       </c>
       <c r="H540" t="n">
         <v>1000</v>
@@ -16232,7 +16232,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G547" t="n">
-        <v>0.908937215805054</v>
+        <v>0.908937275409698</v>
       </c>
       <c r="H547" t="n">
         <v>16000</v>
@@ -16348,7 +16348,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G551" t="n">
-        <v>0.875272870063782</v>
+        <v>0.875272929668427</v>
       </c>
       <c r="H551" t="n">
         <v>4000</v>
@@ -16551,7 +16551,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G558" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H558" t="n">
         <v>137000</v>
@@ -16580,7 +16580,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G559" t="n">
-        <v>0.986274242401123</v>
+        <v>0.986274302005768</v>
       </c>
       <c r="H559" t="n">
         <v>23000</v>
@@ -16754,7 +16754,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G565" t="n">
-        <v>0.94260162115097</v>
+        <v>0.942601561546326</v>
       </c>
       <c r="H565" t="n">
         <v>49000</v>
@@ -16783,7 +16783,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G566" t="n">
-        <v>0.98081511259079</v>
+        <v>0.980815052986145</v>
       </c>
       <c r="H566" t="n">
         <v>25000</v>
@@ -16841,7 +16841,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G568" t="n">
-        <v>0.944421291351318</v>
+        <v>0.944421231746674</v>
       </c>
       <c r="H568" t="n">
         <v>6000</v>
@@ -16928,7 +16928,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G571" t="n">
-        <v>1.25012993812561</v>
+        <v>1.25012981891632</v>
       </c>
       <c r="H571" t="n">
         <v>328000</v>
@@ -17015,7 +17015,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G574" t="n">
-        <v>1.30836009979248</v>
+        <v>1.30835998058319</v>
       </c>
       <c r="H574" t="n">
         <v>231000</v>
@@ -17044,7 +17044,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G575" t="n">
-        <v>1.56675672531128</v>
+        <v>1.56675660610199</v>
       </c>
       <c r="H575" t="n">
         <v>931000</v>
@@ -17102,7 +17102,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>1.97436821460724</v>
+        <v>1.97436833381653</v>
       </c>
       <c r="H577" t="n">
         <v>1358000</v>
@@ -17160,7 +17160,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G579" t="n">
-        <v>1.76146399974823</v>
+        <v>1.76146388053894</v>
       </c>
       <c r="H579" t="n">
         <v>906000</v>
@@ -17189,7 +17189,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G580" t="n">
-        <v>1.77238202095032</v>
+        <v>1.77238214015961</v>
       </c>
       <c r="H580" t="n">
         <v>765000</v>
@@ -17363,7 +17363,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.21547770500183</v>
+        <v>2.21547746658325</v>
       </c>
       <c r="H586" t="n">
         <v>495000</v>
@@ -17392,7 +17392,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.63400745391846</v>
+        <v>2.63400721549988</v>
       </c>
       <c r="H587" t="n">
         <v>835000</v>
@@ -17479,7 +17479,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>2.67040133476257</v>
+        <v>2.67040109634399</v>
       </c>
       <c r="H590" t="n">
         <v>876000</v>
@@ -17566,7 +17566,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G593" t="n">
-        <v>2.83872270584106</v>
+        <v>2.83872294425964</v>
       </c>
       <c r="H593" t="n">
         <v>439000</v>
@@ -17595,7 +17595,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G594" t="n">
-        <v>2.90696120262146</v>
+        <v>2.90696144104004</v>
       </c>
       <c r="H594" t="n">
         <v>251000</v>
@@ -17624,7 +17624,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G595" t="n">
-        <v>2.97065091133118</v>
+        <v>2.9706506729126</v>
       </c>
       <c r="H595" t="n">
         <v>595000</v>
@@ -17740,7 +17740,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>2.76593494415283</v>
+        <v>2.76593518257141</v>
       </c>
       <c r="H599" t="n">
         <v>163000</v>
@@ -17885,7 +17885,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.76593494415283</v>
+        <v>2.76593518257141</v>
       </c>
       <c r="H604" t="n">
         <v>50000</v>
@@ -18001,7 +18001,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>2.52027654647827</v>
+        <v>2.52027630805969</v>
       </c>
       <c r="H608" t="n">
         <v>115000</v>
@@ -18059,7 +18059,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.71134424209595</v>
+        <v>2.71134448051453</v>
       </c>
       <c r="H610" t="n">
         <v>132000</v>
@@ -18117,7 +18117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>2.69314742088318</v>
+        <v>2.6931471824646</v>
       </c>
       <c r="H612" t="n">
         <v>78000</v>
@@ -18146,7 +18146,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.77503371238708</v>
+        <v>2.77503347396851</v>
       </c>
       <c r="H613" t="n">
         <v>162000</v>
@@ -18175,7 +18175,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.76593494415283</v>
+        <v>2.76593518257141</v>
       </c>
       <c r="H614" t="n">
         <v>174000</v>
@@ -18349,7 +18349,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G620" t="n">
-        <v>2.79323053359985</v>
+        <v>2.79323029518127</v>
       </c>
       <c r="H620" t="n">
         <v>99000</v>
@@ -18407,7 +18407,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.54385423660278</v>
+        <v>3.54385447502136</v>
       </c>
       <c r="H622" t="n">
         <v>833000</v>
@@ -18465,7 +18465,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>4.01242542266846</v>
+        <v>4.01242589950562</v>
       </c>
       <c r="H624" t="n">
         <v>972000</v>
@@ -18523,7 +18523,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>3.82135725021362</v>
+        <v>3.8213574886322</v>
       </c>
       <c r="H626" t="n">
         <v>371000</v>
@@ -18552,7 +18552,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>3.73492240905762</v>
+        <v>3.73492217063904</v>
       </c>
       <c r="H627" t="n">
         <v>215000</v>
@@ -18726,7 +18726,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>4.24898624420166</v>
+        <v>4.2489857673645</v>
       </c>
       <c r="H633" t="n">
         <v>78000</v>
@@ -18813,7 +18813,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>4.74030351638794</v>
+        <v>4.74030303955078</v>
       </c>
       <c r="H636" t="n">
         <v>826000</v>
@@ -18871,7 +18871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G638" t="n">
-        <v>5.64105176925659</v>
+        <v>5.64105129241943</v>
       </c>
       <c r="H638" t="n">
         <v>576000</v>
@@ -19132,7 +19132,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>5.8412184715271</v>
+        <v>5.84121799468994</v>
       </c>
       <c r="H647" t="n">
         <v>69000</v>
@@ -19277,7 +19277,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>6.19605875015259</v>
+        <v>6.19605827331543</v>
       </c>
       <c r="H652" t="n">
         <v>166000</v>
@@ -19422,7 +19422,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G657" t="n">
-        <v>6.19605875015259</v>
+        <v>6.19605827331543</v>
       </c>
       <c r="H657" t="n">
         <v>58500</v>
@@ -19538,7 +19538,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G661" t="n">
-        <v>6.28704309463501</v>
+        <v>6.28704357147217</v>
       </c>
       <c r="H661" t="n">
         <v>49000</v>
@@ -19741,7 +19741,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G668" t="n">
-        <v>6.34163379669189</v>
+        <v>6.34163427352905</v>
       </c>
       <c r="H668" t="n">
         <v>29500</v>
@@ -19770,7 +19770,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>6.45081615447998</v>
+        <v>6.45081567764282</v>
       </c>
       <c r="H669" t="n">
         <v>74500</v>
@@ -19828,7 +19828,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>6.34163379669189</v>
+        <v>6.34163427352905</v>
       </c>
       <c r="H671" t="n">
         <v>42500</v>
@@ -19886,7 +19886,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G673" t="n">
-        <v>6.31433916091919</v>
+        <v>6.31433868408203</v>
       </c>
       <c r="H673" t="n">
         <v>22500</v>
@@ -20031,7 +20031,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>5.80482482910156</v>
+        <v>5.8048243522644</v>
       </c>
       <c r="H678" t="n">
         <v>177429</v>
@@ -20147,7 +20147,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>5.55006742477417</v>
+        <v>5.55006694793701</v>
       </c>
       <c r="H682" t="n">
         <v>47228</v>
@@ -20292,7 +20292,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>6.0595817565918</v>
+        <v>6.05958127975464</v>
       </c>
       <c r="H687" t="n">
         <v>134241</v>
@@ -60869,6 +60869,35 @@
         <v>0</v>
       </c>
       <c r="I2086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2087" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2087" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -543,7 +543,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989003777503967</v>
+        <v>0.989003837108612</v>
       </c>
       <c r="H6" t="n">
         <v>114000</v>
@@ -630,7 +630,7 @@
         <v>0.954100012779236</v>
       </c>
       <c r="G9" t="n">
-        <v>0.868085145950317</v>
+        <v>0.868085086345673</v>
       </c>
       <c r="H9" t="n">
         <v>39000</v>
@@ -659,7 +659,7 @@
         <v>0.981899976730347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.893378853797913</v>
+        <v>0.893378794193268</v>
       </c>
       <c r="H10" t="n">
         <v>23000</v>
@@ -1007,7 +1007,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G22" t="n">
-        <v>1.00902044773102</v>
+        <v>1.00902032852173</v>
       </c>
       <c r="H22" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H26" t="n">
         <v>1000</v>
@@ -1152,7 +1152,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G27" t="n">
-        <v>0.983908712863922</v>
+        <v>0.983908593654633</v>
       </c>
       <c r="H27" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G28" t="n">
-        <v>0.983908712863922</v>
+        <v>0.983908593654633</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G29" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H29" t="n">
         <v>34000</v>
@@ -1326,7 +1326,7 @@
         <v>1.08519995212555</v>
       </c>
       <c r="G33" t="n">
-        <v>0.987365961074829</v>
+        <v>0.987366020679474</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G35" t="n">
-        <v>1.02685344219208</v>
+        <v>1.02685332298279</v>
       </c>
       <c r="H35" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G36" t="n">
-        <v>1.02685344219208</v>
+        <v>1.02685332298279</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G37" t="n">
-        <v>1.02685344219208</v>
+        <v>1.02685332298279</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G39" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H39" t="n">
         <v>14000</v>
@@ -1529,7 +1529,7 @@
         <v>1.0654000043869</v>
       </c>
       <c r="G40" t="n">
-        <v>0.969351053237915</v>
+        <v>0.96935111284256</v>
       </c>
       <c r="H40" t="n">
         <v>5000</v>
@@ -1587,7 +1587,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G42" t="n">
-        <v>0.980815052986145</v>
+        <v>0.98081511259079</v>
       </c>
       <c r="H42" t="n">
         <v>55000</v>
@@ -1616,7 +1616,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>0.907117545604706</v>
+        <v>0.907117486000061</v>
       </c>
       <c r="H43" t="n">
         <v>60000</v>
@@ -2138,7 +2138,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G61" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H61" t="n">
         <v>3000</v>
@@ -2660,7 +2660,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>0.826141178607941</v>
+        <v>0.826141119003296</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G80" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H80" t="n">
         <v>21000</v>
@@ -2718,7 +2718,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G81" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G82" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2776,7 +2776,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G83" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>0.802500009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>0.730152249336243</v>
+        <v>0.730152308940887</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G91" t="n">
-        <v>0.713320076465607</v>
+        <v>0.713320136070251</v>
       </c>
       <c r="H91" t="n">
         <v>11000</v>
@@ -3037,7 +3037,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G92" t="n">
-        <v>0.68966406583786</v>
+        <v>0.689664125442505</v>
       </c>
       <c r="H92" t="n">
         <v>36000</v>
@@ -3066,7 +3066,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G93" t="n">
-        <v>0.707861065864563</v>
+        <v>0.707861006259918</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>0.67328679561615</v>
+        <v>0.673286855220795</v>
       </c>
       <c r="H95" t="n">
         <v>2000</v>
@@ -3269,7 +3269,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G100" t="n">
-        <v>0.693303525447845</v>
+        <v>0.693303465843201</v>
       </c>
       <c r="H100" t="n">
         <v>2000</v>
@@ -3298,7 +3298,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G101" t="n">
-        <v>0.704221606254578</v>
+        <v>0.704221665859222</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G102" t="n">
-        <v>0.704221606254578</v>
+        <v>0.704221665859222</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G103" t="n">
-        <v>0.704221606254578</v>
+        <v>0.704221665859222</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G111" t="n">
-        <v>0.580027461051941</v>
+        <v>0.580027520656586</v>
       </c>
       <c r="H111" t="n">
         <v>17000</v>
@@ -3675,7 +3675,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G114" t="n">
-        <v>0.576843023300171</v>
+        <v>0.576843082904816</v>
       </c>
       <c r="H114" t="n">
         <v>3000</v>
@@ -3733,7 +3733,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>0.564105212688446</v>
+        <v>0.564105153083801</v>
       </c>
       <c r="H116" t="n">
         <v>3000</v>
@@ -3820,7 +3820,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G119" t="n">
-        <v>0.624155044555664</v>
+        <v>0.624155104160309</v>
       </c>
       <c r="H119" t="n">
         <v>58000</v>
@@ -3878,7 +3878,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G121" t="n">
-        <v>0.61869603395462</v>
+        <v>0.618695974349976</v>
       </c>
       <c r="H121" t="n">
         <v>8000</v>
@@ -3965,7 +3965,7 @@
         <v>0.676999986171722</v>
       </c>
       <c r="G124" t="n">
-        <v>0.615966439247131</v>
+        <v>0.615966498851776</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G125" t="n">
-        <v>0.595040023326874</v>
+        <v>0.595039963722229</v>
       </c>
       <c r="H125" t="n">
         <v>5000</v>
@@ -4052,7 +4052,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G127" t="n">
-        <v>0.60231876373291</v>
+        <v>0.602318823337555</v>
       </c>
       <c r="H127" t="n">
         <v>12000</v>
@@ -4081,7 +4081,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G128" t="n">
-        <v>0.595949828624725</v>
+        <v>0.595949769020081</v>
       </c>
       <c r="H128" t="n">
         <v>34000</v>
@@ -4110,7 +4110,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G129" t="n">
-        <v>0.595949828624725</v>
+        <v>0.595949769020081</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>0.640532314777374</v>
+        <v>0.640532374382019</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4197,7 +4197,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G132" t="n">
-        <v>0.705131411552429</v>
+        <v>0.705131471157074</v>
       </c>
       <c r="H132" t="n">
         <v>19000</v>
@@ -4226,7 +4226,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G133" t="n">
-        <v>0.723328471183777</v>
+        <v>0.723328411579132</v>
       </c>
       <c r="H133" t="n">
         <v>9000</v>
@@ -4255,7 +4255,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H134" t="n">
         <v>96000</v>
@@ -4284,7 +4284,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G135" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G136" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H142" t="n">
         <v>3000</v>
@@ -4516,7 +4516,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G143" t="n">
-        <v>0.714230000972748</v>
+        <v>0.714229941368103</v>
       </c>
       <c r="H143" t="n">
         <v>46000</v>
@@ -4545,7 +4545,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G144" t="n">
-        <v>0.705131411552429</v>
+        <v>0.705131471157074</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4574,7 +4574,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G145" t="n">
-        <v>0.705131411552429</v>
+        <v>0.705131471157074</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709680736064911</v>
+        <v>0.709680676460266</v>
       </c>
       <c r="H146" t="n">
         <v>1000</v>
@@ -4632,7 +4632,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G147" t="n">
-        <v>0.709680736064911</v>
+        <v>0.709680676460266</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G148" t="n">
-        <v>0.675106525421143</v>
+        <v>0.675106465816498</v>
       </c>
       <c r="H148" t="n">
         <v>6000</v>
@@ -4690,7 +4690,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G149" t="n">
-        <v>0.684204995632172</v>
+        <v>0.684204936027527</v>
       </c>
       <c r="H149" t="n">
         <v>4000</v>
@@ -4719,7 +4719,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G150" t="n">
-        <v>0.684204995632172</v>
+        <v>0.684204936027527</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G151" t="n">
-        <v>0.693303525447845</v>
+        <v>0.693303465843201</v>
       </c>
       <c r="H151" t="n">
         <v>5000</v>
@@ -4777,7 +4777,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G152" t="n">
-        <v>0.693303525447845</v>
+        <v>0.693303465843201</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5009,7 +5009,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G160" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G165" t="n">
-        <v>0.576843023300171</v>
+        <v>0.576843082904816</v>
       </c>
       <c r="H165" t="n">
         <v>93000</v>
@@ -5589,7 +5589,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G180" t="n">
-        <v>0.522252202033997</v>
+        <v>0.522252261638641</v>
       </c>
       <c r="H180" t="n">
         <v>32000</v>
@@ -5618,7 +5618,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G181" t="n">
-        <v>0.53135073184967</v>
+        <v>0.531350672245026</v>
       </c>
       <c r="H181" t="n">
         <v>4000</v>
@@ -5647,7 +5647,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G182" t="n">
-        <v>0.53135073184967</v>
+        <v>0.531350672245026</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G191" t="n">
-        <v>0.471300780773163</v>
+        <v>0.471300810575485</v>
       </c>
       <c r="H191" t="n">
         <v>49000</v>
@@ -5937,7 +5937,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G192" t="n">
-        <v>0.493137151002884</v>
+        <v>0.493137121200562</v>
       </c>
       <c r="H192" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>0.49677649140358</v>
+        <v>0.496776521205902</v>
       </c>
       <c r="H193" t="n">
         <v>6000</v>
@@ -5995,7 +5995,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>0.49677649140358</v>
+        <v>0.496776521205902</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G201" t="n">
-        <v>0.491317451000214</v>
+        <v>0.491317421197891</v>
       </c>
       <c r="H201" t="n">
         <v>22000</v>
@@ -6227,7 +6227,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G202" t="n">
-        <v>0.491317451000214</v>
+        <v>0.491317421197891</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G210" t="n">
-        <v>0.356660038232803</v>
+        <v>0.356660068035126</v>
       </c>
       <c r="H210" t="n">
         <v>120000</v>
@@ -6546,7 +6546,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G213" t="n">
-        <v>0.516793191432953</v>
+        <v>0.516793131828308</v>
       </c>
       <c r="H213" t="n">
         <v>911000</v>
@@ -6749,7 +6749,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G220" t="n">
-        <v>0.658729314804077</v>
+        <v>0.658729255199432</v>
       </c>
       <c r="H220" t="n">
         <v>1878000</v>
@@ -6836,7 +6836,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G223" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H223" t="n">
         <v>4151000</v>
@@ -6923,7 +6923,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H226" t="n">
         <v>434000</v>
@@ -6952,7 +6952,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>0.67328679561615</v>
+        <v>0.673286855220795</v>
       </c>
       <c r="H227" t="n">
         <v>236000</v>
@@ -7126,7 +7126,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G233" t="n">
-        <v>0.753353357315063</v>
+        <v>0.753353416919708</v>
       </c>
       <c r="H233" t="n">
         <v>912000</v>
@@ -7329,7 +7329,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G240" t="n">
-        <v>0.68966406583786</v>
+        <v>0.689664125442505</v>
       </c>
       <c r="H240" t="n">
         <v>121000</v>
@@ -7677,7 +7677,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G252" t="n">
-        <v>0.736976087093353</v>
+        <v>0.736976146697998</v>
       </c>
       <c r="H252" t="n">
         <v>40000</v>
@@ -7706,7 +7706,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G253" t="n">
-        <v>0.749713957309723</v>
+        <v>0.749714016914368</v>
       </c>
       <c r="H253" t="n">
         <v>24000</v>
@@ -7822,7 +7822,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G257" t="n">
-        <v>0.68966406583786</v>
+        <v>0.689664125442505</v>
       </c>
       <c r="H257" t="n">
         <v>15000</v>
@@ -7851,7 +7851,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G258" t="n">
-        <v>0.68602466583252</v>
+        <v>0.686024725437164</v>
       </c>
       <c r="H258" t="n">
         <v>24000</v>
@@ -7880,7 +7880,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>0.67328679561615</v>
+        <v>0.673286855220795</v>
       </c>
       <c r="H259" t="n">
         <v>18000</v>
@@ -8054,7 +8054,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G265" t="n">
-        <v>0.68602466583252</v>
+        <v>0.686024725437164</v>
       </c>
       <c r="H265" t="n">
         <v>29000</v>
@@ -8141,7 +8141,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G268" t="n">
-        <v>0.773370087146759</v>
+        <v>0.773370027542114</v>
       </c>
       <c r="H268" t="n">
         <v>992000</v>
@@ -8344,7 +8344,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G275" t="n">
-        <v>0.74789434671402</v>
+        <v>0.747894287109375</v>
       </c>
       <c r="H275" t="n">
         <v>190000</v>
@@ -8518,7 +8518,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>0.978085696697235</v>
+        <v>0.97808563709259</v>
       </c>
       <c r="H281" t="n">
         <v>1188000</v>
@@ -8547,7 +8547,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G282" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H282" t="n">
         <v>952000</v>
@@ -8605,7 +8605,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G284" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H284" t="n">
         <v>356000</v>
@@ -8634,7 +8634,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H285" t="n">
         <v>1039000</v>
@@ -8721,7 +8721,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G288" t="n">
-        <v>1.41026282310486</v>
+        <v>1.41026294231415</v>
       </c>
       <c r="H288" t="n">
         <v>1203000</v>
@@ -8750,7 +8750,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>1.3465735912323</v>
+        <v>1.34657371044159</v>
       </c>
       <c r="H289" t="n">
         <v>817000</v>
@@ -8924,7 +8924,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H295" t="n">
         <v>209000</v>
@@ -8982,7 +8982,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G297" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H297" t="n">
         <v>294000</v>
@@ -9127,7 +9127,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H302" t="n">
         <v>179000</v>
@@ -9156,7 +9156,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H303" t="n">
         <v>169000</v>
@@ -9243,7 +9243,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G306" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H306" t="n">
         <v>84000</v>
@@ -9272,7 +9272,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H307" t="n">
         <v>56000</v>
@@ -9359,7 +9359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H310" t="n">
         <v>43000</v>
@@ -9475,7 +9475,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H314" t="n">
         <v>31000</v>
@@ -9504,7 +9504,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H315" t="n">
         <v>10000</v>
@@ -9562,7 +9562,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>1.19644892215729</v>
+        <v>1.19644904136658</v>
       </c>
       <c r="H317" t="n">
         <v>70000</v>
@@ -9620,7 +9620,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G319" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H319" t="n">
         <v>36000</v>
@@ -9678,7 +9678,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G321" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H321" t="n">
         <v>22000</v>
@@ -9765,7 +9765,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G324" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H324" t="n">
         <v>16000</v>
@@ -9852,7 +9852,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G327" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H327" t="n">
         <v>195000</v>
@@ -9968,7 +9968,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>1.12821042537689</v>
+        <v>1.1282103061676</v>
       </c>
       <c r="H331" t="n">
         <v>17000</v>
@@ -10026,7 +10026,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G333" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H333" t="n">
         <v>60000</v>
@@ -10171,7 +10171,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G338" t="n">
-        <v>1.12821042537689</v>
+        <v>1.1282103061676</v>
       </c>
       <c r="H338" t="n">
         <v>16000</v>
@@ -10287,7 +10287,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G342" t="n">
-        <v>1.12821042537689</v>
+        <v>1.1282103061676</v>
       </c>
       <c r="H342" t="n">
         <v>27000</v>
@@ -10606,7 +10606,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G353" t="n">
-        <v>0.978085696697235</v>
+        <v>0.97808563709259</v>
       </c>
       <c r="H353" t="n">
         <v>35000</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H354" t="n">
         <v>49000</v>
@@ -10693,7 +10693,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H356" t="n">
         <v>25000</v>
@@ -10780,7 +10780,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06452107429504</v>
+        <v>1.06452095508575</v>
       </c>
       <c r="H359" t="n">
         <v>64000</v>
@@ -10809,7 +10809,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H360" t="n">
         <v>16000</v>
@@ -10867,7 +10867,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G362" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H362" t="n">
         <v>17000</v>
@@ -10896,7 +10896,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G363" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H363" t="n">
         <v>16000</v>
@@ -10925,7 +10925,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G364" t="n">
-        <v>1.03267633914948</v>
+        <v>1.03267645835876</v>
       </c>
       <c r="H364" t="n">
         <v>36000</v>
@@ -10954,7 +10954,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G365" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H365" t="n">
         <v>5000</v>
@@ -11012,7 +11012,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G367" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H367" t="n">
         <v>47000</v>
@@ -11070,7 +11070,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G369" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H369" t="n">
         <v>16000</v>
@@ -11099,7 +11099,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>1.19189965724945</v>
+        <v>1.19189953804016</v>
       </c>
       <c r="H370" t="n">
         <v>393000</v>
@@ -11157,7 +11157,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>1.13275957107544</v>
+        <v>1.13275969028473</v>
       </c>
       <c r="H372" t="n">
         <v>87000</v>
@@ -11186,7 +11186,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>1.10091507434845</v>
+        <v>1.10091495513916</v>
       </c>
       <c r="H373" t="n">
         <v>90000</v>
@@ -11215,7 +11215,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09636569023132</v>
+        <v>1.09636580944061</v>
       </c>
       <c r="H374" t="n">
         <v>40000</v>
@@ -11302,7 +11302,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H377" t="n">
         <v>36000</v>
@@ -11331,7 +11331,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>1.11001348495483</v>
+        <v>1.11001336574554</v>
       </c>
       <c r="H378" t="n">
         <v>22000</v>
@@ -11418,7 +11418,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G381" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H381" t="n">
         <v>32000</v>
@@ -11505,7 +11505,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G384" t="n">
-        <v>1.06907021999359</v>
+        <v>1.06907033920288</v>
       </c>
       <c r="H384" t="n">
         <v>3000</v>
@@ -11621,7 +11621,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.04177498817444</v>
+        <v>1.04177486896515</v>
       </c>
       <c r="H388" t="n">
         <v>24000</v>
@@ -11650,7 +11650,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G389" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H389" t="n">
         <v>14000</v>
@@ -11679,7 +11679,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G390" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11737,7 +11737,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H392" t="n">
         <v>15000</v>
@@ -11795,7 +11795,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G394" t="n">
-        <v>0.991733372211456</v>
+        <v>0.991733312606812</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G395" t="n">
-        <v>0.878912270069122</v>
+        <v>0.878912329673767</v>
       </c>
       <c r="H395" t="n">
         <v>96000</v>
@@ -11853,7 +11853,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G396" t="n">
-        <v>0.83887904882431</v>
+        <v>0.838878989219666</v>
       </c>
       <c r="H396" t="n">
         <v>77000</v>
@@ -11940,7 +11940,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>0.978085696697235</v>
+        <v>0.97808563709259</v>
       </c>
       <c r="H399" t="n">
         <v>136000</v>
@@ -12201,7 +12201,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G408" t="n">
-        <v>0.645991444587708</v>
+        <v>0.645991384983063</v>
       </c>
       <c r="H408" t="n">
         <v>19000</v>
@@ -12317,7 +12317,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H412" t="n">
         <v>150000</v>
@@ -12462,7 +12462,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G417" t="n">
-        <v>0.707861065864563</v>
+        <v>0.707861006259918</v>
       </c>
       <c r="H417" t="n">
         <v>29000</v>
@@ -12491,7 +12491,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>0.691483795642853</v>
+        <v>0.691483736038208</v>
       </c>
       <c r="H418" t="n">
         <v>54000</v>
@@ -12636,7 +12636,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G423" t="n">
-        <v>0.751533627510071</v>
+        <v>0.751533687114716</v>
       </c>
       <c r="H423" t="n">
         <v>21000</v>
@@ -12694,7 +12694,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G425" t="n">
-        <v>0.756992816925049</v>
+        <v>0.756992757320404</v>
       </c>
       <c r="H425" t="n">
         <v>26000</v>
@@ -12984,7 +12984,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G435" t="n">
-        <v>0.901658415794373</v>
+        <v>0.901658475399017</v>
       </c>
       <c r="H435" t="n">
         <v>91000</v>
@@ -13013,7 +13013,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G436" t="n">
-        <v>0.922585010528564</v>
+        <v>0.92258495092392</v>
       </c>
       <c r="H436" t="n">
         <v>16000</v>
@@ -13100,7 +13100,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G439" t="n">
-        <v>0.890740275382996</v>
+        <v>0.890740215778351</v>
       </c>
       <c r="H439" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G443" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H443" t="n">
         <v>41000</v>
@@ -13361,7 +13361,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G448" t="n">
-        <v>1.16460430622101</v>
+        <v>1.16460418701172</v>
       </c>
       <c r="H448" t="n">
         <v>206000</v>
@@ -13622,7 +13622,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G457" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H457" t="n">
         <v>32000</v>
@@ -13680,7 +13680,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G459" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H459" t="n">
         <v>25000</v>
@@ -13767,7 +13767,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G462" t="n">
-        <v>1.06452107429504</v>
+        <v>1.06452095508575</v>
       </c>
       <c r="H462" t="n">
         <v>81000</v>
@@ -14057,7 +14057,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G472" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H472" t="n">
         <v>34000</v>
@@ -14086,7 +14086,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G473" t="n">
-        <v>1.06452107429504</v>
+        <v>1.06452095508575</v>
       </c>
       <c r="H473" t="n">
         <v>40000</v>
@@ -14144,7 +14144,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>1.04450440406799</v>
+        <v>1.04450452327728</v>
       </c>
       <c r="H475" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G481" t="n">
-        <v>0.993552982807159</v>
+        <v>0.993553042411804</v>
       </c>
       <c r="H481" t="n">
         <v>24000</v>
@@ -14347,7 +14347,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G482" t="n">
-        <v>1.04450440406799</v>
+        <v>1.04450452327728</v>
       </c>
       <c r="H482" t="n">
         <v>61000</v>
@@ -14405,7 +14405,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G484" t="n">
-        <v>1.04632413387299</v>
+        <v>1.0463240146637</v>
       </c>
       <c r="H484" t="n">
         <v>17000</v>
@@ -14492,7 +14492,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.00083184242249</v>
+        <v>1.0008317232132</v>
       </c>
       <c r="H487" t="n">
         <v>7000</v>
@@ -14521,7 +14521,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G488" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H488" t="n">
         <v>20000</v>
@@ -14550,7 +14550,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G489" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H489" t="n">
         <v>10000</v>
@@ -14753,7 +14753,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G496" t="n">
-        <v>1.0372257232666</v>
+        <v>1.03722560405731</v>
       </c>
       <c r="H496" t="n">
         <v>5000</v>
@@ -14811,7 +14811,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G498" t="n">
-        <v>1.02266800403595</v>
+        <v>1.02266812324524</v>
       </c>
       <c r="H498" t="n">
         <v>11000</v>
@@ -14869,7 +14869,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G500" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H500" t="n">
         <v>10000</v>
@@ -14956,7 +14956,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G503" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H503" t="n">
         <v>18000</v>
@@ -14985,7 +14985,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>0.933503091335297</v>
+        <v>0.933503150939941</v>
       </c>
       <c r="H504" t="n">
         <v>14000</v>
@@ -15014,7 +15014,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G505" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H505" t="n">
         <v>14000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G506" t="n">
-        <v>0.949880361557007</v>
+        <v>0.949880421161652</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15188,7 +15188,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G511" t="n">
-        <v>0.968077301979065</v>
+        <v>0.96807736158371</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15333,7 +15333,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>0.942601561546326</v>
+        <v>0.94260162115097</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>0.955339372158051</v>
+        <v>0.955339312553406</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>0.955339372158051</v>
+        <v>0.955339312553406</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G520" t="n">
-        <v>0.951700091362</v>
+        <v>0.951700031757355</v>
       </c>
       <c r="H520" t="n">
         <v>26000</v>
@@ -15507,7 +15507,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G522" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H522" t="n">
         <v>4000</v>
@@ -15565,7 +15565,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G524" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15623,7 +15623,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G526" t="n">
-        <v>0.949880361557007</v>
+        <v>0.949880421161652</v>
       </c>
       <c r="H526" t="n">
         <v>9000</v>
@@ -15710,7 +15710,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G529" t="n">
-        <v>0.922585010528564</v>
+        <v>0.92258495092392</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G530" t="n">
-        <v>0.933503091335297</v>
+        <v>0.933503150939941</v>
       </c>
       <c r="H530" t="n">
         <v>15000</v>
@@ -15768,7 +15768,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G531" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H531" t="n">
         <v>4000</v>
@@ -15797,7 +15797,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>0.942601561546326</v>
+        <v>0.94260162115097</v>
       </c>
       <c r="H532" t="n">
         <v>11000</v>
@@ -15826,7 +15826,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>0.933503091335297</v>
+        <v>0.933503150939941</v>
       </c>
       <c r="H533" t="n">
         <v>4000</v>
@@ -15855,7 +15855,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G534" t="n">
-        <v>0.940781950950623</v>
+        <v>0.940781891345978</v>
       </c>
       <c r="H534" t="n">
         <v>11000</v>
@@ -15884,7 +15884,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G535" t="n">
-        <v>0.922585010528564</v>
+        <v>0.92258495092392</v>
       </c>
       <c r="H535" t="n">
         <v>4000</v>
@@ -15942,7 +15942,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G537" t="n">
-        <v>0.878912270069122</v>
+        <v>0.878912329673767</v>
       </c>
       <c r="H537" t="n">
         <v>25000</v>
@@ -15971,7 +15971,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G538" t="n">
-        <v>0.929863631725311</v>
+        <v>0.929863691329956</v>
       </c>
       <c r="H538" t="n">
         <v>48000</v>
@@ -16029,7 +16029,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G540" t="n">
-        <v>0.917125821113586</v>
+        <v>0.917125880718231</v>
       </c>
       <c r="H540" t="n">
         <v>1000</v>
@@ -16232,7 +16232,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G547" t="n">
-        <v>0.908937275409698</v>
+        <v>0.908937215805054</v>
       </c>
       <c r="H547" t="n">
         <v>16000</v>
@@ -16348,7 +16348,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G551" t="n">
-        <v>0.875272929668427</v>
+        <v>0.875272870063782</v>
       </c>
       <c r="H551" t="n">
         <v>4000</v>
@@ -16551,7 +16551,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G558" t="n">
-        <v>0.982634902000427</v>
+        <v>0.982634842395782</v>
       </c>
       <c r="H558" t="n">
         <v>137000</v>
@@ -16580,7 +16580,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G559" t="n">
-        <v>0.986274302005768</v>
+        <v>0.986274242401123</v>
       </c>
       <c r="H559" t="n">
         <v>23000</v>
@@ -16754,7 +16754,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G565" t="n">
-        <v>0.942601561546326</v>
+        <v>0.94260162115097</v>
       </c>
       <c r="H565" t="n">
         <v>49000</v>
@@ -16783,7 +16783,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G566" t="n">
-        <v>0.980815052986145</v>
+        <v>0.98081511259079</v>
       </c>
       <c r="H566" t="n">
         <v>25000</v>
@@ -16841,7 +16841,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G568" t="n">
-        <v>0.944421231746674</v>
+        <v>0.944421291351318</v>
       </c>
       <c r="H568" t="n">
         <v>6000</v>
@@ -16928,7 +16928,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G571" t="n">
-        <v>1.25012981891632</v>
+        <v>1.25012993812561</v>
       </c>
       <c r="H571" t="n">
         <v>328000</v>
@@ -17015,7 +17015,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G574" t="n">
-        <v>1.30835998058319</v>
+        <v>1.30836009979248</v>
       </c>
       <c r="H574" t="n">
         <v>231000</v>
@@ -17044,7 +17044,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G575" t="n">
-        <v>1.56675660610199</v>
+        <v>1.56675672531128</v>
       </c>
       <c r="H575" t="n">
         <v>931000</v>
@@ -17102,7 +17102,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>1.97436833381653</v>
+        <v>1.97436821460724</v>
       </c>
       <c r="H577" t="n">
         <v>1358000</v>
@@ -17160,7 +17160,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G579" t="n">
-        <v>1.76146388053894</v>
+        <v>1.76146399974823</v>
       </c>
       <c r="H579" t="n">
         <v>906000</v>
@@ -17189,7 +17189,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G580" t="n">
-        <v>1.77238214015961</v>
+        <v>1.77238202095032</v>
       </c>
       <c r="H580" t="n">
         <v>765000</v>
@@ -17363,7 +17363,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.21547746658325</v>
+        <v>2.21547770500183</v>
       </c>
       <c r="H586" t="n">
         <v>495000</v>
@@ -17392,7 +17392,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.63400721549988</v>
+        <v>2.63400745391846</v>
       </c>
       <c r="H587" t="n">
         <v>835000</v>
@@ -17479,7 +17479,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>2.67040109634399</v>
+        <v>2.67040133476257</v>
       </c>
       <c r="H590" t="n">
         <v>876000</v>
@@ -17566,7 +17566,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G593" t="n">
-        <v>2.83872294425964</v>
+        <v>2.83872270584106</v>
       </c>
       <c r="H593" t="n">
         <v>439000</v>
@@ -17595,7 +17595,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G594" t="n">
-        <v>2.90696144104004</v>
+        <v>2.90696120262146</v>
       </c>
       <c r="H594" t="n">
         <v>251000</v>
@@ -17624,7 +17624,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G595" t="n">
-        <v>2.9706506729126</v>
+        <v>2.97065091133118</v>
       </c>
       <c r="H595" t="n">
         <v>595000</v>
@@ -17740,7 +17740,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>2.76593518257141</v>
+        <v>2.76593494415283</v>
       </c>
       <c r="H599" t="n">
         <v>163000</v>
@@ -17885,7 +17885,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.76593518257141</v>
+        <v>2.76593494415283</v>
       </c>
       <c r="H604" t="n">
         <v>50000</v>
@@ -18001,7 +18001,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>2.52027630805969</v>
+        <v>2.52027654647827</v>
       </c>
       <c r="H608" t="n">
         <v>115000</v>
@@ -18059,7 +18059,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.71134448051453</v>
+        <v>2.71134424209595</v>
       </c>
       <c r="H610" t="n">
         <v>132000</v>
@@ -18117,7 +18117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>2.6931471824646</v>
+        <v>2.69314742088318</v>
       </c>
       <c r="H612" t="n">
         <v>78000</v>
@@ -18146,7 +18146,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.77503347396851</v>
+        <v>2.77503371238708</v>
       </c>
       <c r="H613" t="n">
         <v>162000</v>
@@ -18175,7 +18175,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.76593518257141</v>
+        <v>2.76593494415283</v>
       </c>
       <c r="H614" t="n">
         <v>174000</v>
@@ -18349,7 +18349,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G620" t="n">
-        <v>2.79323029518127</v>
+        <v>2.79323053359985</v>
       </c>
       <c r="H620" t="n">
         <v>99000</v>
@@ -18407,7 +18407,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.54385447502136</v>
+        <v>3.54385423660278</v>
       </c>
       <c r="H622" t="n">
         <v>833000</v>
@@ -18465,7 +18465,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>4.01242589950562</v>
+        <v>4.01242542266846</v>
       </c>
       <c r="H624" t="n">
         <v>972000</v>
@@ -18523,7 +18523,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>3.8213574886322</v>
+        <v>3.82135725021362</v>
       </c>
       <c r="H626" t="n">
         <v>371000</v>
@@ -18552,7 +18552,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>3.73492217063904</v>
+        <v>3.73492240905762</v>
       </c>
       <c r="H627" t="n">
         <v>215000</v>
@@ -18726,7 +18726,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>4.2489857673645</v>
+        <v>4.24898624420166</v>
       </c>
       <c r="H633" t="n">
         <v>78000</v>
@@ -18813,7 +18813,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>4.74030303955078</v>
+        <v>4.74030351638794</v>
       </c>
       <c r="H636" t="n">
         <v>826000</v>
@@ -18871,7 +18871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G638" t="n">
-        <v>5.64105129241943</v>
+        <v>5.64105176925659</v>
       </c>
       <c r="H638" t="n">
         <v>576000</v>
@@ -19132,7 +19132,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>5.84121799468994</v>
+        <v>5.8412184715271</v>
       </c>
       <c r="H647" t="n">
         <v>69000</v>
@@ -19277,7 +19277,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>6.19605827331543</v>
+        <v>6.19605875015259</v>
       </c>
       <c r="H652" t="n">
         <v>166000</v>
@@ -19422,7 +19422,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G657" t="n">
-        <v>6.19605827331543</v>
+        <v>6.19605875015259</v>
       </c>
       <c r="H657" t="n">
         <v>58500</v>
@@ -19538,7 +19538,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G661" t="n">
-        <v>6.28704357147217</v>
+        <v>6.28704309463501</v>
       </c>
       <c r="H661" t="n">
         <v>49000</v>
@@ -19741,7 +19741,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G668" t="n">
-        <v>6.34163427352905</v>
+        <v>6.34163379669189</v>
       </c>
       <c r="H668" t="n">
         <v>29500</v>
@@ -19770,7 +19770,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>6.45081567764282</v>
+        <v>6.45081615447998</v>
       </c>
       <c r="H669" t="n">
         <v>74500</v>
@@ -19828,7 +19828,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>6.34163427352905</v>
+        <v>6.34163379669189</v>
       </c>
       <c r="H671" t="n">
         <v>42500</v>
@@ -19886,7 +19886,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G673" t="n">
-        <v>6.31433868408203</v>
+        <v>6.31433916091919</v>
       </c>
       <c r="H673" t="n">
         <v>22500</v>
@@ -20031,7 +20031,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>5.8048243522644</v>
+        <v>5.80482482910156</v>
       </c>
       <c r="H678" t="n">
         <v>177429</v>
@@ -20147,7 +20147,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>5.55006694793701</v>
+        <v>5.55006742477417</v>
       </c>
       <c r="H682" t="n">
         <v>47228</v>
@@ -20292,7 +20292,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>6.05958127975464</v>
+        <v>6.0595817565918</v>
       </c>
       <c r="H687" t="n">
         <v>134241</v>
@@ -60898,6 +60898,35 @@
         <v>0</v>
       </c>
       <c r="I2087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2088" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2088" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -60930,6 +60930,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2089">
+      <c r="A2089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2089" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2089" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -60959,6 +60959,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2090">
+      <c r="A2090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2090" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2090" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SCK.MI.xlsx
+++ b/data/SCK.MI.xlsx
@@ -543,7 +543,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.989003837108612</v>
+        <v>0.989003777503967</v>
       </c>
       <c r="H6" t="n">
         <v>114000</v>
@@ -630,7 +630,7 @@
         <v>0.954100012779236</v>
       </c>
       <c r="G9" t="n">
-        <v>0.868085086345673</v>
+        <v>0.868085145950317</v>
       </c>
       <c r="H9" t="n">
         <v>39000</v>
@@ -659,7 +659,7 @@
         <v>0.981899976730347</v>
       </c>
       <c r="G10" t="n">
-        <v>0.893378794193268</v>
+        <v>0.893378853797913</v>
       </c>
       <c r="H10" t="n">
         <v>23000</v>
@@ -1007,7 +1007,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G22" t="n">
-        <v>1.00902032852173</v>
+        <v>1.00902044773102</v>
       </c>
       <c r="H22" t="n">
         <v>12000</v>
@@ -1123,7 +1123,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H26" t="n">
         <v>1000</v>
@@ -1152,7 +1152,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G27" t="n">
-        <v>0.983908593654633</v>
+        <v>0.983908712863922</v>
       </c>
       <c r="H27" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>1.08140003681183</v>
       </c>
       <c r="G28" t="n">
-        <v>0.983908593654633</v>
+        <v>0.983908712863922</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G29" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H29" t="n">
         <v>34000</v>
@@ -1326,7 +1326,7 @@
         <v>1.08519995212555</v>
       </c>
       <c r="G33" t="n">
-        <v>0.987366020679474</v>
+        <v>0.987365961074829</v>
       </c>
       <c r="H33" t="n">
         <v>2000</v>
@@ -1384,7 +1384,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G35" t="n">
-        <v>1.02685332298279</v>
+        <v>1.02685344219208</v>
       </c>
       <c r="H35" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G36" t="n">
-        <v>1.02685332298279</v>
+        <v>1.02685344219208</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>1.12860000133514</v>
       </c>
       <c r="G37" t="n">
-        <v>1.02685332298279</v>
+        <v>1.02685344219208</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G39" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H39" t="n">
         <v>14000</v>
@@ -1529,7 +1529,7 @@
         <v>1.0654000043869</v>
       </c>
       <c r="G40" t="n">
-        <v>0.96935111284256</v>
+        <v>0.969351053237915</v>
       </c>
       <c r="H40" t="n">
         <v>5000</v>
@@ -1587,7 +1587,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G42" t="n">
-        <v>0.98081511259079</v>
+        <v>0.980815052986145</v>
       </c>
       <c r="H42" t="n">
         <v>55000</v>
@@ -1616,7 +1616,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G43" t="n">
-        <v>0.907117486000061</v>
+        <v>0.907117545604706</v>
       </c>
       <c r="H43" t="n">
         <v>60000</v>
@@ -2138,7 +2138,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G61" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H61" t="n">
         <v>3000</v>
@@ -2660,7 +2660,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>0.826141119003296</v>
+        <v>0.826141178607941</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G80" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H80" t="n">
         <v>21000</v>
@@ -2718,7 +2718,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G81" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G82" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2776,7 +2776,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G83" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>0.802500009536743</v>
       </c>
       <c r="G90" t="n">
-        <v>0.730152308940887</v>
+        <v>0.730152249336243</v>
       </c>
       <c r="H90" t="n">
         <v>2000</v>
@@ -3008,7 +3008,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G91" t="n">
-        <v>0.713320136070251</v>
+        <v>0.713320076465607</v>
       </c>
       <c r="H91" t="n">
         <v>11000</v>
@@ -3037,7 +3037,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G92" t="n">
-        <v>0.689664125442505</v>
+        <v>0.68966406583786</v>
       </c>
       <c r="H92" t="n">
         <v>36000</v>
@@ -3066,7 +3066,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G93" t="n">
-        <v>0.707861006259918</v>
+        <v>0.707861065864563</v>
       </c>
       <c r="H93" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G95" t="n">
-        <v>0.673286855220795</v>
+        <v>0.67328679561615</v>
       </c>
       <c r="H95" t="n">
         <v>2000</v>
@@ -3269,7 +3269,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G100" t="n">
-        <v>0.693303465843201</v>
+        <v>0.693303525447845</v>
       </c>
       <c r="H100" t="n">
         <v>2000</v>
@@ -3298,7 +3298,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G101" t="n">
-        <v>0.704221665859222</v>
+        <v>0.704221606254578</v>
       </c>
       <c r="H101" t="n">
         <v>13000</v>
@@ -3327,7 +3327,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G102" t="n">
-        <v>0.704221665859222</v>
+        <v>0.704221606254578</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G103" t="n">
-        <v>0.704221665859222</v>
+        <v>0.704221606254578</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G106" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H106" t="n">
         <v>6000</v>
@@ -3588,7 +3588,7 @@
         <v>0.637499988079071</v>
       </c>
       <c r="G111" t="n">
-        <v>0.580027520656586</v>
+        <v>0.580027461051941</v>
       </c>
       <c r="H111" t="n">
         <v>17000</v>
@@ -3675,7 +3675,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G114" t="n">
-        <v>0.576843082904816</v>
+        <v>0.576843023300171</v>
       </c>
       <c r="H114" t="n">
         <v>3000</v>
@@ -3733,7 +3733,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G116" t="n">
-        <v>0.564105153083801</v>
+        <v>0.564105212688446</v>
       </c>
       <c r="H116" t="n">
         <v>3000</v>
@@ -3820,7 +3820,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G119" t="n">
-        <v>0.624155104160309</v>
+        <v>0.624155044555664</v>
       </c>
       <c r="H119" t="n">
         <v>58000</v>
@@ -3878,7 +3878,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G121" t="n">
-        <v>0.618695974349976</v>
+        <v>0.61869603395462</v>
       </c>
       <c r="H121" t="n">
         <v>8000</v>
@@ -3965,7 +3965,7 @@
         <v>0.676999986171722</v>
       </c>
       <c r="G124" t="n">
-        <v>0.615966498851776</v>
+        <v>0.615966439247131</v>
       </c>
       <c r="H124" t="n">
         <v>3000</v>
@@ -3994,7 +3994,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G125" t="n">
-        <v>0.595039963722229</v>
+        <v>0.595040023326874</v>
       </c>
       <c r="H125" t="n">
         <v>5000</v>
@@ -4052,7 +4052,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G127" t="n">
-        <v>0.602318823337555</v>
+        <v>0.60231876373291</v>
       </c>
       <c r="H127" t="n">
         <v>12000</v>
@@ -4081,7 +4081,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G128" t="n">
-        <v>0.595949769020081</v>
+        <v>0.595949828624725</v>
       </c>
       <c r="H128" t="n">
         <v>34000</v>
@@ -4110,7 +4110,7 @@
         <v>0.654999971389771</v>
       </c>
       <c r="G129" t="n">
-        <v>0.595949769020081</v>
+        <v>0.595949828624725</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>0.640532374382019</v>
+        <v>0.640532314777374</v>
       </c>
       <c r="H131" t="n">
         <v>1000</v>
@@ -4197,7 +4197,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G132" t="n">
-        <v>0.705131471157074</v>
+        <v>0.705131411552429</v>
       </c>
       <c r="H132" t="n">
         <v>19000</v>
@@ -4226,7 +4226,7 @@
         <v>0.795000016689301</v>
       </c>
       <c r="G133" t="n">
-        <v>0.723328411579132</v>
+        <v>0.723328471183777</v>
       </c>
       <c r="H133" t="n">
         <v>9000</v>
@@ -4255,7 +4255,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G134" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H134" t="n">
         <v>96000</v>
@@ -4284,7 +4284,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G135" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G136" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G142" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H142" t="n">
         <v>3000</v>
@@ -4516,7 +4516,7 @@
         <v>0.785000026226044</v>
       </c>
       <c r="G143" t="n">
-        <v>0.714229941368103</v>
+        <v>0.714230000972748</v>
       </c>
       <c r="H143" t="n">
         <v>46000</v>
@@ -4545,7 +4545,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G144" t="n">
-        <v>0.705131471157074</v>
+        <v>0.705131411552429</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4574,7 +4574,7 @@
         <v>0.774999976158142</v>
       </c>
       <c r="G145" t="n">
-        <v>0.705131471157074</v>
+        <v>0.705131411552429</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G146" t="n">
-        <v>0.709680676460266</v>
+        <v>0.709680736064911</v>
       </c>
       <c r="H146" t="n">
         <v>1000</v>
@@ -4632,7 +4632,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G147" t="n">
-        <v>0.709680676460266</v>
+        <v>0.709680736064911</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G148" t="n">
-        <v>0.675106465816498</v>
+        <v>0.675106525421143</v>
       </c>
       <c r="H148" t="n">
         <v>6000</v>
@@ -4690,7 +4690,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G149" t="n">
-        <v>0.684204936027527</v>
+        <v>0.684204995632172</v>
       </c>
       <c r="H149" t="n">
         <v>4000</v>
@@ -4719,7 +4719,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G150" t="n">
-        <v>0.684204936027527</v>
+        <v>0.684204995632172</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G151" t="n">
-        <v>0.693303465843201</v>
+        <v>0.693303525447845</v>
       </c>
       <c r="H151" t="n">
         <v>5000</v>
@@ -4777,7 +4777,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G152" t="n">
-        <v>0.693303465843201</v>
+        <v>0.693303525447845</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G159" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H159" t="n">
         <v>5000</v>
@@ -5009,7 +5009,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G160" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G165" t="n">
-        <v>0.576843082904816</v>
+        <v>0.576843023300171</v>
       </c>
       <c r="H165" t="n">
         <v>93000</v>
@@ -5589,7 +5589,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G180" t="n">
-        <v>0.522252261638641</v>
+        <v>0.522252202033997</v>
       </c>
       <c r="H180" t="n">
         <v>32000</v>
@@ -5618,7 +5618,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G181" t="n">
-        <v>0.531350672245026</v>
+        <v>0.53135073184967</v>
       </c>
       <c r="H181" t="n">
         <v>4000</v>
@@ -5647,7 +5647,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G182" t="n">
-        <v>0.531350672245026</v>
+        <v>0.53135073184967</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G191" t="n">
-        <v>0.471300810575485</v>
+        <v>0.471300780773163</v>
       </c>
       <c r="H191" t="n">
         <v>49000</v>
@@ -5937,7 +5937,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G192" t="n">
-        <v>0.493137121200562</v>
+        <v>0.493137151002884</v>
       </c>
       <c r="H192" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G193" t="n">
-        <v>0.496776521205902</v>
+        <v>0.49677649140358</v>
       </c>
       <c r="H193" t="n">
         <v>6000</v>
@@ -5995,7 +5995,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G194" t="n">
-        <v>0.496776521205902</v>
+        <v>0.49677649140358</v>
       </c>
       <c r="H194" t="n">
         <v>3000</v>
@@ -6198,7 +6198,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G201" t="n">
-        <v>0.491317421197891</v>
+        <v>0.491317451000214</v>
       </c>
       <c r="H201" t="n">
         <v>22000</v>
@@ -6227,7 +6227,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G202" t="n">
-        <v>0.491317421197891</v>
+        <v>0.491317451000214</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G210" t="n">
-        <v>0.356660068035126</v>
+        <v>0.356660038232803</v>
       </c>
       <c r="H210" t="n">
         <v>120000</v>
@@ -6546,7 +6546,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G213" t="n">
-        <v>0.516793131828308</v>
+        <v>0.516793191432953</v>
       </c>
       <c r="H213" t="n">
         <v>911000</v>
@@ -6749,7 +6749,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G220" t="n">
-        <v>0.658729255199432</v>
+        <v>0.658729314804077</v>
       </c>
       <c r="H220" t="n">
         <v>1878000</v>
@@ -6836,7 +6836,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G223" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H223" t="n">
         <v>4151000</v>
@@ -6923,7 +6923,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H226" t="n">
         <v>434000</v>
@@ -6952,7 +6952,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>0.673286855220795</v>
+        <v>0.67328679561615</v>
       </c>
       <c r="H227" t="n">
         <v>236000</v>
@@ -7126,7 +7126,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G233" t="n">
-        <v>0.753353416919708</v>
+        <v>0.753353357315063</v>
       </c>
       <c r="H233" t="n">
         <v>912000</v>
@@ -7329,7 +7329,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G240" t="n">
-        <v>0.689664125442505</v>
+        <v>0.68966406583786</v>
       </c>
       <c r="H240" t="n">
         <v>121000</v>
@@ -7677,7 +7677,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G252" t="n">
-        <v>0.736976146697998</v>
+        <v>0.736976087093353</v>
       </c>
       <c r="H252" t="n">
         <v>40000</v>
@@ -7706,7 +7706,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G253" t="n">
-        <v>0.749714016914368</v>
+        <v>0.749713957309723</v>
       </c>
       <c r="H253" t="n">
         <v>24000</v>
@@ -7822,7 +7822,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G257" t="n">
-        <v>0.689664125442505</v>
+        <v>0.68966406583786</v>
       </c>
       <c r="H257" t="n">
         <v>15000</v>
@@ -7851,7 +7851,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G258" t="n">
-        <v>0.686024725437164</v>
+        <v>0.68602466583252</v>
       </c>
       <c r="H258" t="n">
         <v>24000</v>
@@ -7880,7 +7880,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G259" t="n">
-        <v>0.673286855220795</v>
+        <v>0.67328679561615</v>
       </c>
       <c r="H259" t="n">
         <v>18000</v>
@@ -8054,7 +8054,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G265" t="n">
-        <v>0.686024725437164</v>
+        <v>0.68602466583252</v>
       </c>
       <c r="H265" t="n">
         <v>29000</v>
@@ -8141,7 +8141,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G268" t="n">
-        <v>0.773370027542114</v>
+        <v>0.773370087146759</v>
       </c>
       <c r="H268" t="n">
         <v>992000</v>
@@ -8344,7 +8344,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G275" t="n">
-        <v>0.747894287109375</v>
+        <v>0.74789434671402</v>
       </c>
       <c r="H275" t="n">
         <v>190000</v>
@@ -8518,7 +8518,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G281" t="n">
-        <v>0.97808563709259</v>
+        <v>0.978085696697235</v>
       </c>
       <c r="H281" t="n">
         <v>1188000</v>
@@ -8547,7 +8547,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G282" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H282" t="n">
         <v>952000</v>
@@ -8605,7 +8605,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G284" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H284" t="n">
         <v>356000</v>
@@ -8634,7 +8634,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G285" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H285" t="n">
         <v>1039000</v>
@@ -8721,7 +8721,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G288" t="n">
-        <v>1.41026294231415</v>
+        <v>1.41026282310486</v>
       </c>
       <c r="H288" t="n">
         <v>1203000</v>
@@ -8750,7 +8750,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G289" t="n">
-        <v>1.34657371044159</v>
+        <v>1.3465735912323</v>
       </c>
       <c r="H289" t="n">
         <v>817000</v>
@@ -8924,7 +8924,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G295" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H295" t="n">
         <v>209000</v>
@@ -8982,7 +8982,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G297" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H297" t="n">
         <v>294000</v>
@@ -9127,7 +9127,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G302" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H302" t="n">
         <v>179000</v>
@@ -9156,7 +9156,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G303" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H303" t="n">
         <v>169000</v>
@@ -9243,7 +9243,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G306" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H306" t="n">
         <v>84000</v>
@@ -9272,7 +9272,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G307" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H307" t="n">
         <v>56000</v>
@@ -9359,7 +9359,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G310" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H310" t="n">
         <v>43000</v>
@@ -9475,7 +9475,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G314" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H314" t="n">
         <v>31000</v>
@@ -9504,7 +9504,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G315" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H315" t="n">
         <v>10000</v>
@@ -9562,7 +9562,7 @@
         <v>1.31500005722046</v>
       </c>
       <c r="G317" t="n">
-        <v>1.19644904136658</v>
+        <v>1.19644892215729</v>
       </c>
       <c r="H317" t="n">
         <v>70000</v>
@@ -9620,7 +9620,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G319" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H319" t="n">
         <v>36000</v>
@@ -9678,7 +9678,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G321" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H321" t="n">
         <v>22000</v>
@@ -9765,7 +9765,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G324" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H324" t="n">
         <v>16000</v>
@@ -9852,7 +9852,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G327" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H327" t="n">
         <v>195000</v>
@@ -9968,7 +9968,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>1.1282103061676</v>
+        <v>1.12821042537689</v>
       </c>
       <c r="H331" t="n">
         <v>17000</v>
@@ -10026,7 +10026,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G333" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H333" t="n">
         <v>60000</v>
@@ -10171,7 +10171,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G338" t="n">
-        <v>1.1282103061676</v>
+        <v>1.12821042537689</v>
       </c>
       <c r="H338" t="n">
         <v>16000</v>
@@ -10287,7 +10287,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G342" t="n">
-        <v>1.1282103061676</v>
+        <v>1.12821042537689</v>
       </c>
       <c r="H342" t="n">
         <v>27000</v>
@@ -10606,7 +10606,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G353" t="n">
-        <v>0.97808563709259</v>
+        <v>0.978085696697235</v>
       </c>
       <c r="H353" t="n">
         <v>35000</v>
@@ -10635,7 +10635,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G354" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H354" t="n">
         <v>49000</v>
@@ -10693,7 +10693,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G356" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H356" t="n">
         <v>25000</v>
@@ -10780,7 +10780,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06452095508575</v>
+        <v>1.06452107429504</v>
       </c>
       <c r="H359" t="n">
         <v>64000</v>
@@ -10809,7 +10809,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G360" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H360" t="n">
         <v>16000</v>
@@ -10867,7 +10867,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G362" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H362" t="n">
         <v>17000</v>
@@ -10896,7 +10896,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G363" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H363" t="n">
         <v>16000</v>
@@ -10925,7 +10925,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G364" t="n">
-        <v>1.03267645835876</v>
+        <v>1.03267633914948</v>
       </c>
       <c r="H364" t="n">
         <v>36000</v>
@@ -10954,7 +10954,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G365" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H365" t="n">
         <v>5000</v>
@@ -11012,7 +11012,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G367" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H367" t="n">
         <v>47000</v>
@@ -11070,7 +11070,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G369" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H369" t="n">
         <v>16000</v>
@@ -11099,7 +11099,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G370" t="n">
-        <v>1.19189953804016</v>
+        <v>1.19189965724945</v>
       </c>
       <c r="H370" t="n">
         <v>393000</v>
@@ -11157,7 +11157,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G372" t="n">
-        <v>1.13275969028473</v>
+        <v>1.13275957107544</v>
       </c>
       <c r="H372" t="n">
         <v>87000</v>
@@ -11186,7 +11186,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G373" t="n">
-        <v>1.10091495513916</v>
+        <v>1.10091507434845</v>
       </c>
       <c r="H373" t="n">
         <v>90000</v>
@@ -11215,7 +11215,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09636580944061</v>
+        <v>1.09636569023132</v>
       </c>
       <c r="H374" t="n">
         <v>40000</v>
@@ -11302,7 +11302,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G377" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H377" t="n">
         <v>36000</v>
@@ -11331,7 +11331,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G378" t="n">
-        <v>1.11001336574554</v>
+        <v>1.11001348495483</v>
       </c>
       <c r="H378" t="n">
         <v>22000</v>
@@ -11418,7 +11418,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G381" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H381" t="n">
         <v>32000</v>
@@ -11505,7 +11505,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G384" t="n">
-        <v>1.06907033920288</v>
+        <v>1.06907021999359</v>
       </c>
       <c r="H384" t="n">
         <v>3000</v>
@@ -11621,7 +11621,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G388" t="n">
-        <v>1.04177486896515</v>
+        <v>1.04177498817444</v>
       </c>
       <c r="H388" t="n">
         <v>24000</v>
@@ -11650,7 +11650,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G389" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H389" t="n">
         <v>14000</v>
@@ -11679,7 +11679,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G390" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H390" t="n">
         <v>11000</v>
@@ -11737,7 +11737,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G392" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H392" t="n">
         <v>15000</v>
@@ -11795,7 +11795,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G394" t="n">
-        <v>0.991733312606812</v>
+        <v>0.991733372211456</v>
       </c>
       <c r="H394" t="n">
         <v>24000</v>
@@ -11824,7 +11824,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G395" t="n">
-        <v>0.878912329673767</v>
+        <v>0.878912270069122</v>
       </c>
       <c r="H395" t="n">
         <v>96000</v>
@@ -11853,7 +11853,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G396" t="n">
-        <v>0.838878989219666</v>
+        <v>0.83887904882431</v>
       </c>
       <c r="H396" t="n">
         <v>77000</v>
@@ -11940,7 +11940,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G399" t="n">
-        <v>0.97808563709259</v>
+        <v>0.978085696697235</v>
       </c>
       <c r="H399" t="n">
         <v>136000</v>
@@ -12201,7 +12201,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G408" t="n">
-        <v>0.645991384983063</v>
+        <v>0.645991444587708</v>
       </c>
       <c r="H408" t="n">
         <v>19000</v>
@@ -12317,7 +12317,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G412" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H412" t="n">
         <v>150000</v>
@@ -12462,7 +12462,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G417" t="n">
-        <v>0.707861006259918</v>
+        <v>0.707861065864563</v>
       </c>
       <c r="H417" t="n">
         <v>29000</v>
@@ -12491,7 +12491,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>0.691483736038208</v>
+        <v>0.691483795642853</v>
       </c>
       <c r="H418" t="n">
         <v>54000</v>
@@ -12636,7 +12636,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G423" t="n">
-        <v>0.751533687114716</v>
+        <v>0.751533627510071</v>
       </c>
       <c r="H423" t="n">
         <v>21000</v>
@@ -12694,7 +12694,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G425" t="n">
-        <v>0.756992757320404</v>
+        <v>0.756992816925049</v>
       </c>
       <c r="H425" t="n">
         <v>26000</v>
@@ -12984,7 +12984,7 @@
         <v>0.99099999666214</v>
       </c>
       <c r="G435" t="n">
-        <v>0.901658475399017</v>
+        <v>0.901658415794373</v>
       </c>
       <c r="H435" t="n">
         <v>91000</v>
@@ -13013,7 +13013,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G436" t="n">
-        <v>0.92258495092392</v>
+        <v>0.922585010528564</v>
       </c>
       <c r="H436" t="n">
         <v>16000</v>
@@ -13100,7 +13100,7 @@
         <v>0.978999972343445</v>
       </c>
       <c r="G439" t="n">
-        <v>0.890740215778351</v>
+        <v>0.890740275382996</v>
       </c>
       <c r="H439" t="n">
         <v>2000</v>
@@ -13216,7 +13216,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G443" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H443" t="n">
         <v>41000</v>
@@ -13361,7 +13361,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G448" t="n">
-        <v>1.16460418701172</v>
+        <v>1.16460430622101</v>
       </c>
       <c r="H448" t="n">
         <v>206000</v>
@@ -13622,7 +13622,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G457" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H457" t="n">
         <v>32000</v>
@@ -13680,7 +13680,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G459" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H459" t="n">
         <v>25000</v>
@@ -13767,7 +13767,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G462" t="n">
-        <v>1.06452095508575</v>
+        <v>1.06452107429504</v>
       </c>
       <c r="H462" t="n">
         <v>81000</v>
@@ -14057,7 +14057,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G472" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H472" t="n">
         <v>34000</v>
@@ -14086,7 +14086,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G473" t="n">
-        <v>1.06452095508575</v>
+        <v>1.06452107429504</v>
       </c>
       <c r="H473" t="n">
         <v>40000</v>
@@ -14144,7 +14144,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G475" t="n">
-        <v>1.04450452327728</v>
+        <v>1.04450440406799</v>
       </c>
       <c r="H475" t="n">
         <v>16000</v>
@@ -14318,7 +14318,7 @@
         <v>1.09200000762939</v>
       </c>
       <c r="G481" t="n">
-        <v>0.993553042411804</v>
+        <v>0.993552982807159</v>
       </c>
       <c r="H481" t="n">
         <v>24000</v>
@@ -14347,7 +14347,7 @@
         <v>1.14800000190735</v>
       </c>
       <c r="G482" t="n">
-        <v>1.04450452327728</v>
+        <v>1.04450440406799</v>
       </c>
       <c r="H482" t="n">
         <v>61000</v>
@@ -14405,7 +14405,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G484" t="n">
-        <v>1.0463240146637</v>
+        <v>1.04632413387299</v>
       </c>
       <c r="H484" t="n">
         <v>17000</v>
@@ -14492,7 +14492,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G487" t="n">
-        <v>1.0008317232132</v>
+        <v>1.00083184242249</v>
       </c>
       <c r="H487" t="n">
         <v>7000</v>
@@ -14521,7 +14521,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G488" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H488" t="n">
         <v>20000</v>
@@ -14550,7 +14550,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G489" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H489" t="n">
         <v>10000</v>
@@ -14753,7 +14753,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G496" t="n">
-        <v>1.03722560405731</v>
+        <v>1.0372257232666</v>
       </c>
       <c r="H496" t="n">
         <v>5000</v>
@@ -14811,7 +14811,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G498" t="n">
-        <v>1.02266812324524</v>
+        <v>1.02266800403595</v>
       </c>
       <c r="H498" t="n">
         <v>11000</v>
@@ -14869,7 +14869,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G500" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H500" t="n">
         <v>10000</v>
@@ -14956,7 +14956,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G503" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H503" t="n">
         <v>18000</v>
@@ -14985,7 +14985,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G504" t="n">
-        <v>0.933503150939941</v>
+        <v>0.933503091335297</v>
       </c>
       <c r="H504" t="n">
         <v>14000</v>
@@ -15014,7 +15014,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G505" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H505" t="n">
         <v>14000</v>
@@ -15043,7 +15043,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G506" t="n">
-        <v>0.949880421161652</v>
+        <v>0.949880361557007</v>
       </c>
       <c r="H506" t="n">
         <v>2000</v>
@@ -15188,7 +15188,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G511" t="n">
-        <v>0.96807736158371</v>
+        <v>0.968077301979065</v>
       </c>
       <c r="H511" t="n">
         <v>3000</v>
@@ -15333,7 +15333,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G516" t="n">
-        <v>0.94260162115097</v>
+        <v>0.942601561546326</v>
       </c>
       <c r="H516" t="n">
         <v>6000</v>
@@ -15362,7 +15362,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G517" t="n">
-        <v>0.955339312553406</v>
+        <v>0.955339372158051</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>0.955339312553406</v>
+        <v>0.955339372158051</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>1.0460000038147</v>
       </c>
       <c r="G520" t="n">
-        <v>0.951700031757355</v>
+        <v>0.951700091362</v>
       </c>
       <c r="H520" t="n">
         <v>26000</v>
@@ -15507,7 +15507,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G522" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H522" t="n">
         <v>4000</v>
@@ -15565,7 +15565,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G524" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15623,7 +15623,7 @@
         <v>1.0440000295639</v>
       </c>
       <c r="G526" t="n">
-        <v>0.949880421161652</v>
+        <v>0.949880361557007</v>
       </c>
       <c r="H526" t="n">
         <v>9000</v>
@@ -15710,7 +15710,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G529" t="n">
-        <v>0.92258495092392</v>
+        <v>0.922585010528564</v>
       </c>
       <c r="H529" t="n">
         <v>5000</v>
@@ -15739,7 +15739,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G530" t="n">
-        <v>0.933503150939941</v>
+        <v>0.933503091335297</v>
       </c>
       <c r="H530" t="n">
         <v>15000</v>
@@ -15768,7 +15768,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G531" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H531" t="n">
         <v>4000</v>
@@ -15797,7 +15797,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G532" t="n">
-        <v>0.94260162115097</v>
+        <v>0.942601561546326</v>
       </c>
       <c r="H532" t="n">
         <v>11000</v>
@@ -15826,7 +15826,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>0.933503150939941</v>
+        <v>0.933503091335297</v>
       </c>
       <c r="H533" t="n">
         <v>4000</v>
@@ -15855,7 +15855,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G534" t="n">
-        <v>0.940781891345978</v>
+        <v>0.940781950950623</v>
       </c>
       <c r="H534" t="n">
         <v>11000</v>
@@ -15884,7 +15884,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G535" t="n">
-        <v>0.92258495092392</v>
+        <v>0.922585010528564</v>
       </c>
       <c r="H535" t="n">
         <v>4000</v>
@@ -15942,7 +15942,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G537" t="n">
-        <v>0.878912329673767</v>
+        <v>0.878912270069122</v>
       </c>
       <c r="H537" t="n">
         <v>25000</v>
@@ -15971,7 +15971,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G538" t="n">
-        <v>0.929863691329956</v>
+        <v>0.929863631725311</v>
       </c>
       <c r="H538" t="n">
         <v>48000</v>
@@ -16029,7 +16029,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G540" t="n">
-        <v>0.917125880718231</v>
+        <v>0.917125821113586</v>
       </c>
       <c r="H540" t="n">
         <v>1000</v>
@@ -16232,7 +16232,7 @@
         <v>0.999000012874603</v>
       </c>
       <c r="G547" t="n">
-        <v>0.908937215805054</v>
+        <v>0.908937275409698</v>
       </c>
       <c r="H547" t="n">
         <v>16000</v>
@@ -16348,7 +16348,7 @@
         <v>0.962000012397766</v>
       </c>
       <c r="G551" t="n">
-        <v>0.875272870063782</v>
+        <v>0.875272929668427</v>
       </c>
       <c r="H551" t="n">
         <v>4000</v>
@@ -16551,7 +16551,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G558" t="n">
-        <v>0.982634842395782</v>
+        <v>0.982634902000427</v>
       </c>
       <c r="H558" t="n">
         <v>137000</v>
@@ -16580,7 +16580,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G559" t="n">
-        <v>0.986274242401123</v>
+        <v>0.986274302005768</v>
       </c>
       <c r="H559" t="n">
         <v>23000</v>
@@ -16754,7 +16754,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G565" t="n">
-        <v>0.94260162115097</v>
+        <v>0.942601561546326</v>
       </c>
       <c r="H565" t="n">
         <v>49000</v>
@@ -16783,7 +16783,7 @@
         <v>1.07799994945526</v>
       </c>
       <c r="G566" t="n">
-        <v>0.98081511259079</v>
+        <v>0.980815052986145</v>
       </c>
       <c r="H566" t="n">
         <v>25000</v>
@@ -16841,7 +16841,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G568" t="n">
-        <v>0.944421291351318</v>
+        <v>0.944421231746674</v>
       </c>
       <c r="H568" t="n">
         <v>6000</v>
@@ -16928,7 +16928,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G571" t="n">
-        <v>1.25012993812561</v>
+        <v>1.25012981891632</v>
       </c>
       <c r="H571" t="n">
         <v>328000</v>
@@ -17015,7 +17015,7 @@
         <v>1.43799996376038</v>
       </c>
       <c r="G574" t="n">
-        <v>1.30836009979248</v>
+        <v>1.30835998058319</v>
       </c>
       <c r="H574" t="n">
         <v>231000</v>
@@ -17044,7 +17044,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G575" t="n">
-        <v>1.56675672531128</v>
+        <v>1.56675660610199</v>
       </c>
       <c r="H575" t="n">
         <v>931000</v>
@@ -17102,7 +17102,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G577" t="n">
-        <v>1.97436821460724</v>
+        <v>1.97436833381653</v>
       </c>
       <c r="H577" t="n">
         <v>1358000</v>
@@ -17160,7 +17160,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G579" t="n">
-        <v>1.76146399974823</v>
+        <v>1.76146388053894</v>
       </c>
       <c r="H579" t="n">
         <v>906000</v>
@@ -17189,7 +17189,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G580" t="n">
-        <v>1.77238202095032</v>
+        <v>1.77238214015961</v>
       </c>
       <c r="H580" t="n">
         <v>765000</v>
@@ -17363,7 +17363,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G586" t="n">
-        <v>2.21547770500183</v>
+        <v>2.21547746658325</v>
       </c>
       <c r="H586" t="n">
         <v>495000</v>
@@ -17392,7 +17392,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G587" t="n">
-        <v>2.63400745391846</v>
+        <v>2.63400721549988</v>
       </c>
       <c r="H587" t="n">
         <v>835000</v>
@@ -17479,7 +17479,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G590" t="n">
-        <v>2.67040133476257</v>
+        <v>2.67040109634399</v>
       </c>
       <c r="H590" t="n">
         <v>876000</v>
@@ -17566,7 +17566,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G593" t="n">
-        <v>2.83872270584106</v>
+        <v>2.83872294425964</v>
       </c>
       <c r="H593" t="n">
         <v>439000</v>
@@ -17595,7 +17595,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G594" t="n">
-        <v>2.90696120262146</v>
+        <v>2.90696144104004</v>
       </c>
       <c r="H594" t="n">
         <v>251000</v>
@@ -17624,7 +17624,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G595" t="n">
-        <v>2.97065091133118</v>
+        <v>2.9706506729126</v>
       </c>
       <c r="H595" t="n">
         <v>595000</v>
@@ -17740,7 +17740,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>2.76593494415283</v>
+        <v>2.76593518257141</v>
       </c>
       <c r="H599" t="n">
         <v>163000</v>
@@ -17885,7 +17885,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>2.76593494415283</v>
+        <v>2.76593518257141</v>
       </c>
       <c r="H604" t="n">
         <v>50000</v>
@@ -18001,7 +18001,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G608" t="n">
-        <v>2.52027654647827</v>
+        <v>2.52027630805969</v>
       </c>
       <c r="H608" t="n">
         <v>115000</v>
@@ -18059,7 +18059,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G610" t="n">
-        <v>2.71134424209595</v>
+        <v>2.71134448051453</v>
       </c>
       <c r="H610" t="n">
         <v>132000</v>
@@ -18117,7 +18117,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>2.69314742088318</v>
+        <v>2.6931471824646</v>
       </c>
       <c r="H612" t="n">
         <v>78000</v>
@@ -18146,7 +18146,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>2.77503371238708</v>
+        <v>2.77503347396851</v>
       </c>
       <c r="H613" t="n">
         <v>162000</v>
@@ -18175,7 +18175,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>2.76593494415283</v>
+        <v>2.76593518257141</v>
       </c>
       <c r="H614" t="n">
         <v>174000</v>
@@ -18349,7 +18349,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G620" t="n">
-        <v>2.79323053359985</v>
+        <v>2.79323029518127</v>
       </c>
       <c r="H620" t="n">
         <v>99000</v>
@@ -18407,7 +18407,7 @@
         <v>3.89499998092651</v>
       </c>
       <c r="G622" t="n">
-        <v>3.54385423660278</v>
+        <v>3.54385447502136</v>
       </c>
       <c r="H622" t="n">
         <v>833000</v>
@@ -18465,7 +18465,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G624" t="n">
-        <v>4.01242542266846</v>
+        <v>4.01242589950562</v>
       </c>
       <c r="H624" t="n">
         <v>972000</v>
@@ -18523,7 +18523,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G626" t="n">
-        <v>3.82135725021362</v>
+        <v>3.8213574886322</v>
       </c>
       <c r="H626" t="n">
         <v>371000</v>
@@ -18552,7 +18552,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G627" t="n">
-        <v>3.73492240905762</v>
+        <v>3.73492217063904</v>
       </c>
       <c r="H627" t="n">
         <v>215000</v>
@@ -18726,7 +18726,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G633" t="n">
-        <v>4.24898624420166</v>
+        <v>4.2489857673645</v>
       </c>
       <c r="H633" t="n">
         <v>78000</v>
@@ -18813,7 +18813,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>4.74030351638794</v>
+        <v>4.74030303955078</v>
       </c>
       <c r="H636" t="n">
         <v>826000</v>
@@ -18871,7 +18871,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G638" t="n">
-        <v>5.64105176925659</v>
+        <v>5.64105129241943</v>
       </c>
       <c r="H638" t="n">
         <v>576000</v>
@@ -19132,7 +19132,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>5.8412184715271</v>
+        <v>5.84121799468994</v>
       </c>
       <c r="H647" t="n">
         <v>69000</v>
@@ -19277,7 +19277,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>6.19605875015259</v>
+        <v>6.19605827331543</v>
       </c>
       <c r="H652" t="n">
         <v>166000</v>
@@ -19422,7 +19422,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G657" t="n">
-        <v>6.19605875015259</v>
+        <v>6.19605827331543</v>
       </c>
       <c r="H657" t="n">
         <v>58500</v>
@@ -19538,7 +19538,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G661" t="n">
-        <v>6.28704309463501</v>
+        <v>6.28704357147217</v>
       </c>
       <c r="H661" t="n">
         <v>49000</v>
@@ -19741,7 +19741,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G668" t="n">
-        <v>6.34163379669189</v>
+        <v>6.34163427352905</v>
       </c>
       <c r="H668" t="n">
         <v>29500</v>
@@ -19770,7 +19770,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G669" t="n">
-        <v>6.45081615447998</v>
+        <v>6.45081567764282</v>
       </c>
       <c r="H669" t="n">
         <v>74500</v>
@@ -19828,7 +19828,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G671" t="n">
-        <v>6.34163379669189</v>
+        <v>6.34163427352905</v>
       </c>
       <c r="H671" t="n">
         <v>42500</v>
@@ -19886,7 +19886,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G673" t="n">
-        <v>6.31433916091919</v>
+        <v>6.31433868408203</v>
       </c>
       <c r="H673" t="n">
         <v>22500</v>
@@ -20031,7 +20031,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>5.80482482910156</v>
+        <v>5.8048243522644</v>
       </c>
       <c r="H678" t="n">
         <v>177429</v>
@@ -20147,7 +20147,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G682" t="n">
-        <v>5.55006742477417</v>
+        <v>5.55006694793701</v>
       </c>
       <c r="H682" t="n">
         <v>47228</v>
@@ -20292,7 +20292,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>6.0595817565918</v>
+        <v>6.05958127975464</v>
       </c>
       <c r="H687" t="n">
         <v>134241</v>
@@ -60985,6 +60985,35 @@
         <v>0</v>
       </c>
       <c r="I2090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2091" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>0.939000010490417</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2091" t="s">
         <v>9</v>
       </c>
     </row>
